--- a/entertainment-os/docs/Entertainment-OS-Workbook.xlsx
+++ b/entertainment-os/docs/Entertainment-OS-Workbook.xlsx
@@ -16,7 +16,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Spend by Person" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Expense Reports" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Split Calculator" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flow" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locations" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalog" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flow" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,9 +28,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
-    <numFmt numFmtId="165" formatCode="$#,##0.00;($#,##0.00);&quot;-&quot;"/>
-    <numFmt numFmtId="166" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
+    <numFmt numFmtId="164" formatCode="[&gt;=10000000]&quot;₹&quot;##\,##\,##\,##0;[&gt;=100000]&quot;₹&quot;##\,##\,##0;&quot;₹&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="0.0%;(0.0%);&quot;-&quot;"/>
+    <numFmt numFmtId="166" formatCode="&quot;₹&quot;#,##0.00;-&quot;₹&quot;#,##0.00;&quot;-&quot;"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -41,7 +43,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="002F6B3F"/>
+      <color rgb="004B3FD1"/>
       <sz val="16"/>
     </font>
     <font>
@@ -80,7 +82,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F6B3F"/>
+        <fgColor rgb="004B3FD1"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,15 +128,15 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -528,24 +530,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="118" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Entertainment OS — Operations Workbook</t>
+          <t>Entertainment OS — Operations Workbook (India)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Northwind Partners · 2026-Q3 · generated from the demo run of the agent pipeline</t>
+          <t>Northwind India Pvt. Ltd. · FY27 Q2 (Jul–Sep 2026) · all amounts in Indian rupees (₹) · generated from the demo run of the agent pipeline</t>
         </is>
       </c>
     </row>
@@ -569,7 +571,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Approval thresholds and per-attendee caps (inputs). Change them to re-run the approval logic on every booking.</t>
+          <t>Approval thresholds and per-person caps in ₹ (inputs). Change them and every booking's approval chain recalculates.</t>
         </is>
       </c>
     </row>
@@ -581,7 +583,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Every booking: who booked it, category, vendor, amount, who pays, status and the approval chain the policy requires.</t>
+          <t>Every booking: request, city, who booked it, who pays, seats/tickets, amount, status and the approval chain the policy requires.</t>
         </is>
       </c>
     </row>
@@ -617,7 +619,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Personally-paid spend claimed back, with routing to Finance, HR or Benefits.</t>
+          <t>Personally-paid spend claimed back, routed to Finance, HR or Benefits.</t>
         </is>
       </c>
     </row>
@@ -629,7 +631,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Family &amp; friends expenses with each member's share (Splitwise style).</t>
+          <t>Family &amp; friends expenses with each member's share (Splitwise style) and UPI settlements.</t>
         </is>
       </c>
     </row>
@@ -641,7 +643,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Net balance per member = paid − share ± settlements.</t>
+          <t>Net balance per member = paid − share + settlements sent − settlements received.</t>
         </is>
       </c>
     </row>
@@ -660,58 +662,82 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
+          <t>Locations</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Country → State → City list used by the location picker. 'Other' lets anyone type a place that isn't listed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Catalog</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Films now showing, their languages and formats, and the event types listed near you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>Flow</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Step-by-step flow of a request through the agents.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Blue text</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Hard-coded input — safe to edit.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Yellow fill</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Key assumption / cell you are expected to fill in.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Key assumption / cell you are expected to change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Black text</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Formula — do not overwrite.</t>
         </is>
@@ -728,12 +754,2338 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C114"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>State / region</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Visakhapatnam</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Vijayawada</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Tirupati</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Andhra Pradesh</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Guntur</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Arunachal Pradesh</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Itanagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Arunachal Pradesh</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Tawang</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Guwahati</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Dibrugarh</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Silchar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Patna</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Gaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Bihar</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>Bhagalpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Raipur</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Bilaspur</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Chhattisgarh</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Bhilai</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Panaji</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Margao</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Goa</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Ahmedabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Surat</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>Vadodara</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Rajkot</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Gujarat</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>Gandhinagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Gurugram</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Faridabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>Panipat</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Ambala</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Himachal Pradesh</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Shimla</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Himachal Pradesh</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Manali</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Himachal Pradesh</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Dharamshala</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Jharkhand</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>Ranchi</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Jharkhand</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Jamshedpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Jharkhand</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Dhanbad</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Mysuru</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Mangaluru</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Hubballi</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Kochi</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Kozhikode</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>Kerala</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Thrissur</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Indore</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Bhopal</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Gwalior</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Madhya Pradesh</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Jabalpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Pune</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Nagpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Nashik</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>Thane</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B53" s="8" t="inlineStr">
+        <is>
+          <t>Manipur</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Imphal</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>Meghalaya</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>Shillong</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B55" s="8" t="inlineStr">
+        <is>
+          <t>Mizoram</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Aizawl</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Nagaland</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
+        <is>
+          <t>Kohima</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B57" s="8" t="inlineStr">
+        <is>
+          <t>Nagaland</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>Dimapur</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>Bhubaneswar</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B59" s="8" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>Cuttack</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B60" s="8" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>Puri</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>Ludhiana</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>Amritsar</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B63" s="8" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="C63" s="8" t="inlineStr">
+        <is>
+          <t>Jalandhar</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>Punjab</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>Mohali</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B65" s="8" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>Jaipur</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>Udaipur</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>Jodhpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Rajasthan</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>Kota</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B69" s="8" t="inlineStr">
+        <is>
+          <t>Sikkim</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>Gangtok</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>Chennai</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B71" s="8" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>Madurai</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>Tamil Nadu</t>
+        </is>
+      </c>
+      <c r="C73" s="8" t="inlineStr">
+        <is>
+          <t>Tiruchirappalli</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C75" s="8" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="C76" s="8" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B77" s="8" t="inlineStr">
+        <is>
+          <t>Tripura</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>Agartala</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>Lucknow</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="C79" s="8" t="inlineStr">
+        <is>
+          <t>Noida</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B80" s="8" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="C80" s="8" t="inlineStr">
+        <is>
+          <t>Kanpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B81" s="8" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>Varanasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>Agra</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>Uttar Pradesh</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>Ghaziabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>Dehradun</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>Rishikesh</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>Uttarakhand</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>Nainital</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>Siliguri</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="inlineStr">
+        <is>
+          <t>Durgapur</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="inlineStr">
+        <is>
+          <t>West Bengal</t>
+        </is>
+      </c>
+      <c r="C90" s="8" t="inlineStr">
+        <is>
+          <t>Darjeeling</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t>Andaman and Nicobar Islands</t>
+        </is>
+      </c>
+      <c r="C91" s="8" t="inlineStr">
+        <is>
+          <t>Port Blair</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="inlineStr">
+        <is>
+          <t>Chandigarh</t>
+        </is>
+      </c>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>Chandigarh</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="inlineStr">
+        <is>
+          <t>Dadra and Nagar Haveli and Daman and Diu</t>
+        </is>
+      </c>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>Daman</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B94" s="8" t="inlineStr">
+        <is>
+          <t>Dadra and Nagar Haveli and Daman and Diu</t>
+        </is>
+      </c>
+      <c r="C94" s="8" t="inlineStr">
+        <is>
+          <t>Silvassa</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B95" s="8" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="C95" s="8" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B96" s="8" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="C96" s="8" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B97" s="8" t="inlineStr">
+        <is>
+          <t>Jammu and Kashmir</t>
+        </is>
+      </c>
+      <c r="C97" s="8" t="inlineStr">
+        <is>
+          <t>Srinagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B98" s="8" t="inlineStr">
+        <is>
+          <t>Jammu and Kashmir</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>Jammu</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>Ladakh</t>
+        </is>
+      </c>
+      <c r="C99" s="8" t="inlineStr">
+        <is>
+          <t>Leh</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="inlineStr">
+        <is>
+          <t>Lakshadweep</t>
+        </is>
+      </c>
+      <c r="C100" s="8" t="inlineStr">
+        <is>
+          <t>Kavaratti</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B101" s="8" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B102" s="8" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="8" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B104" s="8" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B105" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B107" s="8" t="inlineStr">
+        <is>
+          <t>Scotland</t>
+        </is>
+      </c>
+      <c r="C107" s="8" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="C108" s="8" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="C109" s="8" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="C110" s="8" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="15" t="inlineStr">
+        <is>
+          <t>Other…</t>
+        </is>
+      </c>
+      <c r="B112" s="15" t="inlineStr">
+        <is>
+          <t>Other… (type any state or region)</t>
+        </is>
+      </c>
+      <c r="C112" s="15" t="inlineStr">
+        <is>
+          <t>Other… (type any city)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>36 Indian states &amp; union territories, 100 Indian cities, plus 4 other countries. Every level has an 'Other' option for typing a place that isn't listed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Genre</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Certificate</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Runtime</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>Formats</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Monsoon Letters</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Romance · Drama</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>2h 18m</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>2D / Recliner</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Rakshak: The Last Guard</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>Hindi</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>2h 34m</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>2D / IMAX / Recliner</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Marina Nights</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Tamil</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Thriller</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>2h 26m</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>2D / Recliner</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Pushpaka Rising</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Telugu</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Action · Fantasy</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>2h 51m</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>2D / 3D / IMAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Kaveri Diaries</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Kannada</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="inlineStr">
+        <is>
+          <t>Drama</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>2h 05m</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>2D</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Orbit 9</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Sci-fi</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>UA</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>2h 12m</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>2D / 3D / IMAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Ponnonam</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Malayalam</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>Family · Comedy</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>2h 10m</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>2D</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Kolkata Noir</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Bengali</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Mystery</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>2h 01m</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>2D / Recliner</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Event types near you</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>music</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Comedy</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>comedy</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Theatre</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>theatre</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Food &amp; festivals</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Films, cinemas, events and venues are fictional demo data, generated for whichever city is selected.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
   </cols>
@@ -761,7 +3113,7 @@
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
-          <t>Where to see it in the app</t>
+          <t>Where in the app</t>
         </is>
       </c>
     </row>
@@ -776,17 +3128,17 @@
       </c>
       <c r="C2" s="23" t="inlineStr">
         <is>
-          <t>Types a plain-language request, e.g. 'Client dinner for 4 tonight'.</t>
+          <t>Picks Country → State → City (or 'Other' and types it), then browses Movies / Events / Dining, or types a request such as '3 tickets for Orbit 9 IMAX tomorrow evening'.</t>
         </is>
       </c>
       <c r="D2" s="23" t="inlineStr">
         <is>
-          <t>Free-text request</t>
+          <t>Location + request</t>
         </is>
       </c>
       <c r="E2" s="23" t="inlineStr">
         <is>
-          <t>Home → prompt</t>
+          <t>Top bar · Discover</t>
         </is>
       </c>
     </row>
@@ -801,7 +3153,7 @@
       </c>
       <c r="C3" s="23" t="inlineStr">
         <is>
-          <t>Detects category, date, guests, vendor, price, funding (company / reimbursable / personal / shared) and purpose; matches a family or friends group.</t>
+          <t>Works out the category, city, date and party size; picks the show and best seats together, the event and ticket tier, or the venue; prices it; proposes who pays; matches a family/friends group.</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
@@ -811,7 +3163,7 @@
       </c>
       <c r="E3" s="23" t="inlineStr">
         <is>
-          <t>Home → Booking draft</t>
+          <t>Checkout · Concierge</t>
         </is>
       </c>
     </row>
@@ -826,7 +3178,7 @@
       </c>
       <c r="C4" s="23" t="inlineStr">
         <is>
-          <t>Checks the right pot: department quarterly budget, wellbeing stipend or personal monthly budget.</t>
+          <t>Checks the right pot: department quarterly budget, wellbeing allowance or personal monthly budget.</t>
         </is>
       </c>
       <c r="D4" s="23" t="inlineStr">
@@ -836,7 +3188,7 @@
       </c>
       <c r="E4" s="23" t="inlineStr">
         <is>
-          <t>Home → Budget agent card</t>
+          <t>Checkout · Budget agent</t>
         </is>
       </c>
     </row>
@@ -851,7 +3203,7 @@
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>Builds the approval chain from thresholds, caps, compliance categories and budget status; removes self-approval.</t>
+          <t>Builds the approval chain from ₹ thresholds, per-person caps, compliance categories and budget status; removes self-approval.</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
@@ -861,7 +3213,7 @@
       </c>
       <c r="E5" s="23" t="inlineStr">
         <is>
-          <t>Home → Policy agent card</t>
+          <t>Checkout · Policy agent</t>
         </is>
       </c>
     </row>
@@ -876,7 +3228,7 @@
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>Edits anything on the draft and confirms.</t>
+          <t>Changes who pays / group / purpose if needed and confirms. Movie seats are held immediately.</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
@@ -901,7 +3253,7 @@
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>Notifies the current approver; each approves or rejects in order; rejection stops the chain.</t>
+          <t>Notifies the current approver; each approves or rejects in order; a rejection stops the chain and releases seats.</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
@@ -911,7 +3263,7 @@
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>Approvals inbox</t>
+          <t>Approvals</t>
         </is>
       </c>
     </row>
@@ -926,7 +3278,7 @@
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>Confirms with the vendor, issues a confirmation code, sends invites.</t>
+          <t>Confirms with the cinema, organiser or venue and issues m-tickets, e-tickets or a confirmation code.</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -951,7 +3303,7 @@
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>Shared bookings: posts to the group ledger, computes shares, balances and fewest-payments settle-up.</t>
+          <t>Shared bookings: posts to the group ledger, computes shares, balances and a fewest-payments settle-up (UPI).</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -976,7 +3328,7 @@
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>Reimbursable bookings: become claimable; report drafted with receipts and routed to Finance, HR or Benefits.</t>
+          <t>Reimbursable bookings become claimable; the report is drafted with receipts and routed to Finance, HR or Benefits.</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -1001,7 +3353,7 @@
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
-          <t>Final approval; reimbursement paid; stipend reduced for wellbeing claims.</t>
+          <t>Final approval; reimbursement with payroll; the wellbeing allowance is reduced for wellbeing claims.</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -1026,25 +3378,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="84" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Policy inputs</t>
+          <t>Policy inputs (₹)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Source: src/seed.js → POLICY (values set by Finance). Edit the blue cells.</t>
+          <t>Source: src/seed.js → POLICY, set by Finance. Edit the blue cells; Bookings column T recalculates.</t>
         </is>
       </c>
     </row>
@@ -1056,7 +3408,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Value (₹)</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -1068,11 +3420,11 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Auto-approve limit ($)</t>
+          <t>Auto-approve limit</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>250</v>
+        <v>20000</v>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
@@ -1083,11 +3435,11 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Manager limit ($)</t>
+          <t>Manager limit</t>
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>2500</v>
+        <v>200000</v>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
@@ -1098,11 +3450,11 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Department head limit ($)</t>
+          <t>Department head limit</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>10000</v>
+        <v>800000</v>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
@@ -1113,7 +3465,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Per-attendee caps (company spend)</t>
+          <t>Per-person caps (company money)</t>
         </is>
       </c>
     </row>
@@ -1125,7 +3477,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>Cap per attendee ($)</t>
+          <t>Cap per person (₹)</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1137,109 +3489,124 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>reservations</t>
+          <t>movies</t>
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Reservations</t>
+          <t>Movies</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>pdr</t>
+          <t>events</t>
         </is>
       </c>
       <c r="B13" s="11" t="n">
-        <v>175</v>
+        <v>25000</v>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Private dining &amp; events</t>
+          <t>Events &amp; live</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>catering</t>
+          <t>reservations</t>
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>60</v>
+        <v>4000</v>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Catering</t>
+          <t>Dining</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>pdr</t>
         </is>
       </c>
       <c r="B15" s="11" t="n">
-        <v>600</v>
+        <v>5000</v>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Sports &amp; live events</t>
+          <t>Private dining</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>gifting</t>
+          <t>catering</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>100</v>
+        <v>1500</v>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Gifting &amp; merch</t>
+          <t>Catering</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
+          <t>gifting</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Gifting &amp; merch</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
           <t>experiences</t>
         </is>
       </c>
-      <c r="B17" s="11" t="n">
-        <v>900</v>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="B18" s="11" t="n">
+        <v>40000</v>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Experiences</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Compliance review categories (client-facing only)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>sports</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>events</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
         <is>
           <t>gifting</t>
         </is>
@@ -1256,29 +3623,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="9" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
-    <col width="8" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
     <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
-    <col width="44" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="42" customWidth="1" min="20" max="20"/>
+    <col width="50" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="26" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1304,82 +3675,102 @@
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
+          <t>Request (as typed)</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>Vendor</t>
-        </is>
-      </c>
       <c r="G1" s="7" t="inlineStr">
         <is>
+          <t>Vendor / venue</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
           <t>Booked by</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Dept</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Who pays</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Client-facing</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
-        <is>
-          <t>Guests</t>
-        </is>
-      </c>
-      <c r="M1" s="7" t="inlineStr">
-        <is>
-          <t>Amount ($)</t>
-        </is>
-      </c>
-      <c r="N1" s="7" t="inlineStr">
-        <is>
-          <t>Per attendee ($)</t>
-        </is>
-      </c>
       <c r="O1" s="7" t="inlineStr">
         <is>
-          <t>Cap ($)</t>
+          <t>Guests / tickets</t>
         </is>
       </c>
       <c r="P1" s="7" t="inlineStr">
         <is>
+          <t>Amount (₹)</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>Per person (₹)</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>Cap (₹)</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
           <t>Over cap?</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="inlineStr">
+      <c r="T1" s="7" t="inlineStr">
         <is>
           <t>Policy approval chain</t>
         </is>
       </c>
-      <c r="R1" s="7" t="inlineStr">
-        <is>
-          <t>Approvals in system</t>
-        </is>
-      </c>
-      <c r="S1" s="7" t="inlineStr">
+      <c r="U1" s="7" t="inlineStr">
+        <is>
+          <t>Approvals recorded by the agents</t>
+        </is>
+      </c>
+      <c r="V1" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="T1" s="7" t="inlineStr">
+      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>Group</t>
+        </is>
+      </c>
+      <c r="X1" s="7" t="inlineStr">
+        <is>
+          <t>Seats / tickets</t>
         </is>
       </c>
     </row>
@@ -1391,7 +3782,7 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
@@ -1401,77 +3792,93 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Reservations</t>
+          <t>Dining</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>Client dinner for 4 tonight</t>
+          <t>Client dinner for 6 tonight</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>Quince</t>
+          <t>Client dinner for 6 tonight</t>
         </is>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Bengaluru Supper Club</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>Ananya Iyer</t>
+        </is>
+      </c>
+      <c r="K2" s="8" t="inlineStr">
+        <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="I2" s="12" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>corporate</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="M2" s="8" t="inlineStr">
         <is>
           <t>business</t>
         </is>
       </c>
-      <c r="K2" s="12" t="inlineStr">
+      <c r="N2" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L2" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M2" s="13" t="n">
-        <v>560</v>
-      </c>
-      <c r="N2" s="14">
-        <f>IF(L2&gt;0,M2/L2,0)</f>
-        <v/>
-      </c>
-      <c r="O2" s="15">
-        <f>IFERROR(INDEX(Policy!$B$12:$B$17,MATCH(C2,Policy!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="P2" s="8">
-        <f>IF(AND(I2="corporate",N2&gt;O2),"Yes","No")</f>
-        <v/>
-      </c>
-      <c r="Q2" s="8">
-        <f>IF(I2&lt;&gt;"corporate","None (not company money)",IF(AND(M2&lt;=Policy!$B$5,P2="No"),"Auto-approved","Manager"&amp;IF(OR(M2&gt;Policy!$B$6,P2="Yes")," → Dept head","")&amp;IF(AND(K2="Yes",OR(C2=Policy!$A$20,C2=Policy!$A$21))," → Compliance","")&amp;IF(M2&gt;Policy!$B$7," → Finance","")))</f>
-        <v/>
-      </c>
-      <c r="R2" s="8" t="inlineStr">
-        <is>
-          <t>Manager (Raj Patel: pending)</t>
-        </is>
-      </c>
-      <c r="S2" s="8" t="inlineStr">
+      <c r="O2" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="P2" s="11" t="n">
+        <v>21000</v>
+      </c>
+      <c r="Q2" s="13">
+        <f>IF(O2&gt;0,P2/O2,0)</f>
+        <v/>
+      </c>
+      <c r="R2" s="13">
+        <f>IFERROR(INDEX(Policy!$B$12:$B$18,MATCH(C2,Policy!$A$12:$A$18,0)),0)</f>
+        <v/>
+      </c>
+      <c r="S2" s="8">
+        <f>IF(AND(L2="corporate",Q2&gt;R2),"Yes","No")</f>
+        <v/>
+      </c>
+      <c r="T2" s="8">
+        <f>IF(L2&lt;&gt;"corporate","None (not company money)",IF(AND(P2&lt;=Policy!$B$5,S2="No"),"Auto-approved","Manager"&amp;IF(OR(P2&gt;Policy!$B$6,S2="Yes")," → Dept head","")&amp;IF(AND(N2="Yes",OR(C2=Policy!$A$21,C2=Policy!$A$22))," → Compliance","")&amp;IF(P2&gt;Policy!$B$7," → Finance","")))</f>
+        <v/>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>Manager (Rahul Mehta: pending)</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
         <is>
           <t>pending_approval</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr"/>
+      <c r="W2" s="8" t="inlineStr"/>
+      <c r="X2" s="8" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -1491,77 +3898,93 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Private dining &amp; events</t>
+          <t>Private dining</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>Private room for 30 on Oct 15 for the client summit</t>
+          <t>Private dining room for 30 on 15 Oct for the client summit</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>The Morris — Private Room</t>
+          <t>Private dining room for 30 on 15 Oct for the client summit</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>Raj Patel</t>
+          <t>The Mumbai Grand — Private Dining Room</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>Rahul Mehta</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="I3" s="12" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>corporate</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t>business</t>
         </is>
       </c>
-      <c r="K3" s="12" t="inlineStr">
+      <c r="N3" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L3" s="12" t="n">
+      <c r="O3" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="M3" s="13" t="n">
-        <v>4500</v>
-      </c>
-      <c r="N3" s="14">
-        <f>IF(L3&gt;0,M3/L3,0)</f>
-        <v/>
-      </c>
-      <c r="O3" s="15">
-        <f>IFERROR(INDEX(Policy!$B$12:$B$17,MATCH(C3,Policy!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="P3" s="8">
-        <f>IF(AND(I3="corporate",N3&gt;O3),"Yes","No")</f>
-        <v/>
-      </c>
-      <c r="Q3" s="8">
-        <f>IF(I3&lt;&gt;"corporate","None (not company money)",IF(AND(M3&lt;=Policy!$B$5,P3="No"),"Auto-approved","Manager"&amp;IF(OR(M3&gt;Policy!$B$6,P3="Yes")," → Dept head","")&amp;IF(AND(K3="Yes",OR(C3=Policy!$A$20,C3=Policy!$A$21))," → Compliance","")&amp;IF(M3&gt;Policy!$B$7," → Finance","")))</f>
-        <v/>
-      </c>
-      <c r="R3" s="8" t="inlineStr">
-        <is>
-          <t>Manager (Elena Brooks: approved)</t>
-        </is>
-      </c>
-      <c r="S3" s="8" t="inlineStr">
+      <c r="P3" s="11" t="n">
+        <v>135000</v>
+      </c>
+      <c r="Q3" s="13">
+        <f>IF(O3&gt;0,P3/O3,0)</f>
+        <v/>
+      </c>
+      <c r="R3" s="13">
+        <f>IFERROR(INDEX(Policy!$B$12:$B$18,MATCH(C3,Policy!$A$12:$A$18,0)),0)</f>
+        <v/>
+      </c>
+      <c r="S3" s="8">
+        <f>IF(AND(L3="corporate",Q3&gt;R3),"Yes","No")</f>
+        <v/>
+      </c>
+      <c r="T3" s="8">
+        <f>IF(L3&lt;&gt;"corporate","None (not company money)",IF(AND(P3&lt;=Policy!$B$5,S3="No"),"Auto-approved","Manager"&amp;IF(OR(P3&gt;Policy!$B$6,S3="Yes")," → Dept head","")&amp;IF(AND(N3="Yes",OR(C3=Policy!$A$21,C3=Policy!$A$22))," → Compliance","")&amp;IF(P3&gt;Policy!$B$7," → Finance","")))</f>
+        <v/>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>Manager (Priya Sharma: approved)</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="T3" s="8" t="inlineStr"/>
+      <c r="W3" s="8" t="inlineStr"/>
+      <c r="X3" s="8" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -1586,72 +4009,88 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Offsite lunch catering for 120 people on Oct 2</t>
+          <t>Offsite lunch catering for 120 people on 2 Oct</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>Bi-Rite Catering</t>
+          <t>Offsite lunch catering for 120 people on 2 Oct</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>Kim Nguyen</t>
+          <t>Bengaluru Feast Co.</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Neha Gupta</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
           <t>people</t>
         </is>
       </c>
-      <c r="I4" s="12" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>corporate</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>morale</t>
         </is>
       </c>
-      <c r="K4" s="12" t="inlineStr">
+      <c r="N4" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L4" s="12" t="n">
+      <c r="O4" s="12" t="n">
         <v>120</v>
       </c>
-      <c r="M4" s="13" t="n">
-        <v>4560</v>
-      </c>
-      <c r="N4" s="14">
-        <f>IF(L4&gt;0,M4/L4,0)</f>
-        <v/>
-      </c>
-      <c r="O4" s="15">
-        <f>IFERROR(INDEX(Policy!$B$12:$B$17,MATCH(C4,Policy!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="P4" s="8">
-        <f>IF(AND(I4="corporate",N4&gt;O4),"Yes","No")</f>
-        <v/>
-      </c>
-      <c r="Q4" s="8">
-        <f>IF(I4&lt;&gt;"corporate","None (not company money)",IF(AND(M4&lt;=Policy!$B$5,P4="No"),"Auto-approved","Manager"&amp;IF(OR(M4&gt;Policy!$B$6,P4="Yes")," → Dept head","")&amp;IF(AND(K4="Yes",OR(C4=Policy!$A$20,C4=Policy!$A$21))," → Compliance","")&amp;IF(M4&gt;Policy!$B$7," → Finance","")))</f>
-        <v/>
-      </c>
-      <c r="R4" s="8" t="inlineStr">
-        <is>
-          <t>Manager (Sam Okafor: approved)</t>
-        </is>
-      </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="P4" s="11" t="n">
+        <v>168000</v>
+      </c>
+      <c r="Q4" s="13">
+        <f>IF(O4&gt;0,P4/O4,0)</f>
+        <v/>
+      </c>
+      <c r="R4" s="13">
+        <f>IFERROR(INDEX(Policy!$B$12:$B$18,MATCH(C4,Policy!$A$12:$A$18,0)),0)</f>
+        <v/>
+      </c>
+      <c r="S4" s="8">
+        <f>IF(AND(L4="corporate",Q4&gt;R4),"Yes","No")</f>
+        <v/>
+      </c>
+      <c r="T4" s="8">
+        <f>IF(L4&lt;&gt;"corporate","None (not company money)",IF(AND(P4&lt;=Policy!$B$5,S4="No"),"Auto-approved","Manager"&amp;IF(OR(P4&gt;Policy!$B$6,S4="Yes")," → Dept head","")&amp;IF(AND(N4="Yes",OR(C4=Policy!$A$21,C4=Policy!$A$22))," → Compliance","")&amp;IF(P4&gt;Policy!$B$7," → Finance","")))</f>
+        <v/>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>Manager (Vikram Singh: approved)</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr"/>
+      <c r="W4" s="8" t="inlineStr"/>
+      <c r="X4" s="8" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -1661,87 +4100,107 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-11-04</t>
+          <t>2026-11-21</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>events</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Sports &amp; live events</t>
+          <t>Events &amp; live</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Suite at the Warriors game for 12 clients Nov 4</t>
+          <t>Corporate box at the T20 night for 10 clients</t>
         </is>
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Chase Center — Warriors Suite</t>
+          <t>T20 Night: Mumbai Chargers vs Capital Kings · 10 × Corporate box (per seat)</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t>Elena Brooks</t>
+          <t>Mumbai Cricket Stadium</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
+        <is>
+          <t>Maharashtra</t>
+        </is>
+      </c>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>Priya Sharma</t>
+        </is>
+      </c>
+      <c r="K5" s="8" t="inlineStr">
+        <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="I5" s="12" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>corporate</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>business</t>
         </is>
       </c>
-      <c r="K5" s="12" t="inlineStr">
+      <c r="N5" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L5" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="M5" s="13" t="n">
-        <v>6600</v>
-      </c>
-      <c r="N5" s="14">
-        <f>IF(L5&gt;0,M5/L5,0)</f>
-        <v/>
-      </c>
-      <c r="O5" s="15">
-        <f>IFERROR(INDEX(Policy!$B$12:$B$17,MATCH(C5,Policy!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="P5" s="8">
-        <f>IF(AND(I5="corporate",N5&gt;O5),"Yes","No")</f>
-        <v/>
-      </c>
-      <c r="Q5" s="8">
-        <f>IF(I5&lt;&gt;"corporate","None (not company money)",IF(AND(M5&lt;=Policy!$B$5,P5="No"),"Auto-approved","Manager"&amp;IF(OR(M5&gt;Policy!$B$6,P5="Yes")," → Dept head","")&amp;IF(AND(K5="Yes",OR(C5=Policy!$A$20,C5=Policy!$A$21))," → Compliance","")&amp;IF(M5&gt;Policy!$B$7," → Finance","")))</f>
-        <v/>
-      </c>
-      <c r="R5" s="8" t="inlineStr">
-        <is>
-          <t>Manager (Sam Okafor: approved) → Compliance (Ivy Walsh: pending)</t>
-        </is>
-      </c>
-      <c r="S5" s="8" t="inlineStr">
+      <c r="O5" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="P5" s="11" t="n">
+        <v>150000</v>
+      </c>
+      <c r="Q5" s="13">
+        <f>IF(O5&gt;0,P5/O5,0)</f>
+        <v/>
+      </c>
+      <c r="R5" s="13">
+        <f>IFERROR(INDEX(Policy!$B$12:$B$18,MATCH(C5,Policy!$A$12:$A$18,0)),0)</f>
+        <v/>
+      </c>
+      <c r="S5" s="8">
+        <f>IF(AND(L5="corporate",Q5&gt;R5),"Yes","No")</f>
+        <v/>
+      </c>
+      <c r="T5" s="8">
+        <f>IF(L5&lt;&gt;"corporate","None (not company money)",IF(AND(P5&lt;=Policy!$B$5,S5="No"),"Auto-approved","Manager"&amp;IF(OR(P5&gt;Policy!$B$6,S5="Yes")," → Dept head","")&amp;IF(AND(N5="Yes",OR(C5=Policy!$A$21,C5=Policy!$A$22))," → Compliance","")&amp;IF(P5&gt;Policy!$B$7," → Finance","")))</f>
+        <v/>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>Manager (Vikram Singh: approved) → Compliance (Meera Joshi: pending)</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
         <is>
           <t>pending_approval</t>
         </is>
       </c>
-      <c r="T5" s="8" t="inlineStr"/>
+      <c r="W5" s="8" t="inlineStr"/>
+      <c r="X5" s="8" t="inlineStr">
+        <is>
+          <t>10 × Corporate box (per seat)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -1751,7 +4210,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>2026-12-01</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -1766,72 +4225,88 @@
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>Holiday gifts for 40 clients Dec 1</t>
+          <t>Diwali gift hampers for 60 clients on 20 Oct</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Goldbelly Gift Boxes</t>
+          <t>Diwali gift hampers for 60 clients on 20 Oct</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Bengaluru Artisan Hampers</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>Ananya Iyer</t>
+        </is>
+      </c>
+      <c r="K6" s="8" t="inlineStr">
+        <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>corporate</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>business</t>
         </is>
       </c>
-      <c r="K6" s="12" t="inlineStr">
+      <c r="N6" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L6" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="M6" s="13" t="n">
-        <v>3400</v>
-      </c>
-      <c r="N6" s="14">
-        <f>IF(L6&gt;0,M6/L6,0)</f>
-        <v/>
-      </c>
-      <c r="O6" s="15">
-        <f>IFERROR(INDEX(Policy!$B$12:$B$17,MATCH(C6,Policy!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="P6" s="8">
-        <f>IF(AND(I6="corporate",N6&gt;O6),"Yes","No")</f>
-        <v/>
-      </c>
-      <c r="Q6" s="8">
-        <f>IF(I6&lt;&gt;"corporate","None (not company money)",IF(AND(M6&lt;=Policy!$B$5,P6="No"),"Auto-approved","Manager"&amp;IF(OR(M6&gt;Policy!$B$6,P6="Yes")," → Dept head","")&amp;IF(AND(K6="Yes",OR(C6=Policy!$A$20,C6=Policy!$A$21))," → Compliance","")&amp;IF(M6&gt;Policy!$B$7," → Finance","")))</f>
-        <v/>
-      </c>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t>Manager (Raj Patel: pending) → Department head (Elena Brooks: pending) → Compliance (Ivy Walsh: pending)</t>
-        </is>
-      </c>
-      <c r="S6" s="8" t="inlineStr">
+      <c r="O6" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="P6" s="11" t="n">
+        <v>210000</v>
+      </c>
+      <c r="Q6" s="13">
+        <f>IF(O6&gt;0,P6/O6,0)</f>
+        <v/>
+      </c>
+      <c r="R6" s="13">
+        <f>IFERROR(INDEX(Policy!$B$12:$B$18,MATCH(C6,Policy!$A$12:$A$18,0)),0)</f>
+        <v/>
+      </c>
+      <c r="S6" s="8">
+        <f>IF(AND(L6="corporate",Q6&gt;R6),"Yes","No")</f>
+        <v/>
+      </c>
+      <c r="T6" s="8">
+        <f>IF(L6&lt;&gt;"corporate","None (not company money)",IF(AND(P6&lt;=Policy!$B$5,S6="No"),"Auto-approved","Manager"&amp;IF(OR(P6&gt;Policy!$B$6,S6="Yes")," → Dept head","")&amp;IF(AND(N6="Yes",OR(C6=Policy!$A$21,C6=Policy!$A$22))," → Compliance","")&amp;IF(P6&gt;Policy!$B$7," → Finance","")))</f>
+        <v/>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>Manager (Rahul Mehta: pending) → Department head (Priya Sharma: pending) → Compliance (Meera Joshi: pending)</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t>pending_approval</t>
         </is>
       </c>
-      <c r="T6" s="8" t="inlineStr"/>
+      <c r="W6" s="8" t="inlineStr"/>
+      <c r="X6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -1841,7 +4316,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -1856,72 +4331,88 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>Team offsite in Napa for 8 on Oct 20</t>
+          <t>Team offsite retreat for 12 on 24 Oct</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Napa Valley Wine Retreat</t>
+          <t>Team offsite retreat for 12 on 24 Oct</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>Ana Ruiz</t>
+          <t>Coorg coffee-estate retreat</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Kavya Nair</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
           <t>product</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="L7" s="12" t="inlineStr">
         <is>
           <t>corporate</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>morale</t>
         </is>
       </c>
-      <c r="K7" s="12" t="inlineStr">
+      <c r="N7" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L7" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M7" s="13" t="n">
-        <v>3600</v>
-      </c>
-      <c r="N7" s="14">
-        <f>IF(L7&gt;0,M7/L7,0)</f>
-        <v/>
-      </c>
-      <c r="O7" s="15">
-        <f>IFERROR(INDEX(Policy!$B$12:$B$17,MATCH(C7,Policy!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="P7" s="8">
-        <f>IF(AND(I7="corporate",N7&gt;O7),"Yes","No")</f>
-        <v/>
-      </c>
-      <c r="Q7" s="8">
-        <f>IF(I7&lt;&gt;"corporate","None (not company money)",IF(AND(M7&lt;=Policy!$B$5,P7="No"),"Auto-approved","Manager"&amp;IF(OR(M7&gt;Policy!$B$6,P7="Yes")," → Dept head","")&amp;IF(AND(K7="Yes",OR(C7=Policy!$A$20,C7=Policy!$A$21))," → Compliance","")&amp;IF(M7&gt;Policy!$B$7," → Finance","")))</f>
-        <v/>
-      </c>
-      <c r="R7" s="8" t="inlineStr">
-        <is>
-          <t>Manager (Sam Okafor: approved)</t>
-        </is>
-      </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="O7" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="P7" s="11" t="n">
+        <v>264000</v>
+      </c>
+      <c r="Q7" s="13">
+        <f>IF(O7&gt;0,P7/O7,0)</f>
+        <v/>
+      </c>
+      <c r="R7" s="13">
+        <f>IFERROR(INDEX(Policy!$B$12:$B$18,MATCH(C7,Policy!$A$12:$A$18,0)),0)</f>
+        <v/>
+      </c>
+      <c r="S7" s="8">
+        <f>IF(AND(L7="corporate",Q7&gt;R7),"Yes","No")</f>
+        <v/>
+      </c>
+      <c r="T7" s="8">
+        <f>IF(L7&lt;&gt;"corporate","None (not company money)",IF(AND(P7&lt;=Policy!$B$5,S7="No"),"Auto-approved","Manager"&amp;IF(OR(P7&gt;Policy!$B$6,S7="Yes")," → Dept head","")&amp;IF(AND(N7="Yes",OR(C7=Policy!$A$21,C7=Policy!$A$22))," → Compliance","")&amp;IF(P7&gt;Policy!$B$7," → Finance","")))</f>
+        <v/>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>Manager (Vikram Singh: approved)</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr"/>
+      <c r="W7" s="8" t="inlineStr"/>
+      <c r="X7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -1931,87 +4422,107 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>reservations</t>
+          <t>movies</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Reservations</t>
+          <t>Movies</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Team drinks for 3 Friday</t>
+          <t>Team movie night for 8 — Pushpaka Rising IMAX Friday evening</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Quince</t>
+          <t>Pushpaka Rising · IMAX · 8 tickets</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Leo Martins</t>
+          <t>Starlight Multiplex — Hyderabad Central</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="J8" s="8" t="inlineStr">
+        <is>
+          <t>Arjun Reddy</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="inlineStr">
+        <is>
           <t>product</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="L8" s="12" t="inlineStr">
         <is>
           <t>corporate</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="M8" s="8" t="inlineStr">
         <is>
           <t>morale</t>
         </is>
       </c>
-      <c r="K8" s="12" t="inlineStr">
+      <c r="N8" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L8" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>420</v>
-      </c>
-      <c r="N8" s="14">
-        <f>IF(L8&gt;0,M8/L8,0)</f>
-        <v/>
-      </c>
-      <c r="O8" s="15">
-        <f>IFERROR(INDEX(Policy!$B$12:$B$17,MATCH(C8,Policy!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="P8" s="8">
-        <f>IF(AND(I8="corporate",N8&gt;O8),"Yes","No")</f>
-        <v/>
-      </c>
-      <c r="Q8" s="8">
-        <f>IF(I8&lt;&gt;"corporate","None (not company money)",IF(AND(M8&lt;=Policy!$B$5,P8="No"),"Auto-approved","Manager"&amp;IF(OR(M8&gt;Policy!$B$6,P8="Yes")," → Dept head","")&amp;IF(AND(K8="Yes",OR(C8=Policy!$A$20,C8=Policy!$A$21))," → Compliance","")&amp;IF(M8&gt;Policy!$B$7," → Finance","")))</f>
-        <v/>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
-        <is>
-          <t>Manager (Ana Ruiz: pending)</t>
-        </is>
-      </c>
-      <c r="S8" s="8" t="inlineStr">
-        <is>
-          <t>pending_approval</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr"/>
+      <c r="O8" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="P8" s="11" t="n">
+        <v>4160</v>
+      </c>
+      <c r="Q8" s="13">
+        <f>IF(O8&gt;0,P8/O8,0)</f>
+        <v/>
+      </c>
+      <c r="R8" s="13">
+        <f>IFERROR(INDEX(Policy!$B$12:$B$18,MATCH(C8,Policy!$A$12:$A$18,0)),0)</f>
+        <v/>
+      </c>
+      <c r="S8" s="8">
+        <f>IF(AND(L8="corporate",Q8&gt;R8),"Yes","No")</f>
+        <v/>
+      </c>
+      <c r="T8" s="8">
+        <f>IF(L8&lt;&gt;"corporate","None (not company money)",IF(AND(P8&lt;=Policy!$B$5,S8="No"),"Auto-approved","Manager"&amp;IF(OR(P8&gt;Policy!$B$6,S8="Yes")," → Dept head","")&amp;IF(AND(N8="Yes",OR(C8=Policy!$A$21,C8=Policy!$A$22))," → Compliance","")&amp;IF(P8&gt;Policy!$B$7," → Finance","")))</f>
+        <v/>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr"/>
+      <c r="X8" s="8" t="inlineStr">
+        <is>
+          <t>IMAX · H4, H5, H6, H7, H8, H9, H10, H11</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -2026,84 +4537,104 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>reservations</t>
+          <t>movies</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Reservations</t>
+          <t>Movies</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Dinner with my family Saturday — split with the family</t>
+          <t>Kaveri Diaries movie with my family Saturday evening</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Quince</t>
+          <t>Kaveri Diaries · 2D · 3 tickets</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Starlight Multiplex — Bengaluru Central</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>Ananya Iyer</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr">
+      <c r="L9" s="12" t="inlineStr">
         <is>
           <t>shared</t>
         </is>
       </c>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="M9" s="8" t="inlineStr">
         <is>
           <t>personal</t>
         </is>
       </c>
-      <c r="K9" s="12" t="inlineStr">
+      <c r="N9" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L9" s="12" t="n">
+      <c r="O9" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M9" s="13" t="n">
-        <v>420</v>
-      </c>
-      <c r="N9" s="14">
-        <f>IF(L9&gt;0,M9/L9,0)</f>
-        <v/>
-      </c>
-      <c r="O9" s="15">
-        <f>IFERROR(INDEX(Policy!$B$12:$B$17,MATCH(C9,Policy!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="P9" s="8">
-        <f>IF(AND(I9="corporate",N9&gt;O9),"Yes","No")</f>
-        <v/>
-      </c>
-      <c r="Q9" s="8">
-        <f>IF(I9&lt;&gt;"corporate","None (not company money)",IF(AND(M9&lt;=Policy!$B$5,P9="No"),"Auto-approved","Manager"&amp;IF(OR(M9&gt;Policy!$B$6,P9="Yes")," → Dept head","")&amp;IF(AND(K9="Yes",OR(C9=Policy!$A$20,C9=Policy!$A$21))," → Compliance","")&amp;IF(M9&gt;Policy!$B$7," → Finance","")))</f>
-        <v/>
-      </c>
-      <c r="R9" s="8" t="inlineStr">
+      <c r="P9" s="11" t="n">
+        <v>660</v>
+      </c>
+      <c r="Q9" s="13">
+        <f>IF(O9&gt;0,P9/O9,0)</f>
+        <v/>
+      </c>
+      <c r="R9" s="13">
+        <f>IFERROR(INDEX(Policy!$B$12:$B$18,MATCH(C9,Policy!$A$12:$A$18,0)),0)</f>
+        <v/>
+      </c>
+      <c r="S9" s="8">
+        <f>IF(AND(L9="corporate",Q9&gt;R9),"Yes","No")</f>
+        <v/>
+      </c>
+      <c r="T9" s="8">
+        <f>IF(L9&lt;&gt;"corporate","None (not company money)",IF(AND(P9&lt;=Policy!$B$5,S9="No"),"Auto-approved","Manager"&amp;IF(OR(P9&gt;Policy!$B$6,S9="Yes")," → Dept head","")&amp;IF(AND(N9="Yes",OR(C9=Policy!$A$21,C9=Policy!$A$22))," → Compliance","")&amp;IF(P9&gt;Policy!$B$7," → Finance","")))</f>
+        <v/>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="S9" s="8" t="inlineStr">
+      <c r="V9" s="8" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>Chen family</t>
+      <c r="W9" s="8" t="inlineStr">
+        <is>
+          <t>Iyer family</t>
+        </is>
+      </c>
+      <c r="X9" s="8" t="inlineStr">
+        <is>
+          <t>2D · G1, G2, G3</t>
         </is>
       </c>
     </row>
@@ -2115,89 +4646,109 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>sports</t>
+          <t>events</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Sports &amp; live events</t>
+          <t>Events &amp; live</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Giants game tickets with friends for 4 Sunday, split</t>
+          <t>Stand-up comedy with friends this weekend, split</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Oracle Park — Giants Club Seats</t>
+          <t>Stand-up Saturday · 4 × Regular</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>Leo Martins</t>
+          <t>The Laugh Store, Hyderabad</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>Arjun Reddy</t>
+        </is>
+      </c>
+      <c r="K10" s="8" t="inlineStr">
+        <is>
           <t>product</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="L10" s="12" t="inlineStr">
         <is>
           <t>shared</t>
         </is>
       </c>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="M10" s="8" t="inlineStr">
         <is>
           <t>personal</t>
         </is>
       </c>
-      <c r="K10" s="12" t="inlineStr">
+      <c r="N10" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L10" s="12" t="n">
+      <c r="O10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="M10" s="13" t="n">
-        <v>720</v>
-      </c>
-      <c r="N10" s="14">
-        <f>IF(L10&gt;0,M10/L10,0)</f>
-        <v/>
-      </c>
-      <c r="O10" s="15">
-        <f>IFERROR(INDEX(Policy!$B$12:$B$17,MATCH(C10,Policy!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="P10" s="8">
-        <f>IF(AND(I10="corporate",N10&gt;O10),"Yes","No")</f>
-        <v/>
-      </c>
-      <c r="Q10" s="8">
-        <f>IF(I10&lt;&gt;"corporate","None (not company money)",IF(AND(M10&lt;=Policy!$B$5,P10="No"),"Auto-approved","Manager"&amp;IF(OR(M10&gt;Policy!$B$6,P10="Yes")," → Dept head","")&amp;IF(AND(K10="Yes",OR(C10=Policy!$A$20,C10=Policy!$A$21))," → Compliance","")&amp;IF(M10&gt;Policy!$B$7," → Finance","")))</f>
-        <v/>
-      </c>
-      <c r="R10" s="8" t="inlineStr">
+      <c r="P10" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q10" s="13">
+        <f>IF(O10&gt;0,P10/O10,0)</f>
+        <v/>
+      </c>
+      <c r="R10" s="13">
+        <f>IFERROR(INDEX(Policy!$B$12:$B$18,MATCH(C10,Policy!$A$12:$A$18,0)),0)</f>
+        <v/>
+      </c>
+      <c r="S10" s="8">
+        <f>IF(AND(L10="corporate",Q10&gt;R10),"Yes","No")</f>
+        <v/>
+      </c>
+      <c r="T10" s="8">
+        <f>IF(L10&lt;&gt;"corporate","None (not company money)",IF(AND(P10&lt;=Policy!$B$5,S10="No"),"Auto-approved","Manager"&amp;IF(OR(P10&gt;Policy!$B$6,S10="Yes")," → Dept head","")&amp;IF(AND(N10="Yes",OR(C10=Policy!$A$21,C10=Policy!$A$22))," → Compliance","")&amp;IF(P10&gt;Policy!$B$7," → Finance","")))</f>
+        <v/>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="S10" s="8" t="inlineStr">
+      <c r="V10" s="8" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>Weekend crew</t>
+      <c r="W10" s="8" t="inlineStr">
+        <is>
+          <t>Weekend gang</t>
+        </is>
+      </c>
+      <c r="X10" s="8" t="inlineStr">
+        <is>
+          <t>4 × Regular</t>
         </is>
       </c>
     </row>
@@ -2209,7 +4760,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -2219,7 +4770,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Reservations</t>
+          <t>Dining</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -2229,67 +4780,83 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>Quince</t>
+          <t>Client lunch for 2 tomorrow, I will pay and expense it</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Bengaluru Supper Club</t>
         </is>
       </c>
       <c r="H11" s="8" t="inlineStr">
         <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>Ananya Iyer</t>
+        </is>
+      </c>
+      <c r="K11" s="8" t="inlineStr">
+        <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="I11" s="12" t="inlineStr">
+      <c r="L11" s="12" t="inlineStr">
         <is>
           <t>reimbursable</t>
         </is>
       </c>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="M11" s="8" t="inlineStr">
         <is>
           <t>business</t>
         </is>
       </c>
-      <c r="K11" s="12" t="inlineStr">
+      <c r="N11" s="12" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="O11" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="M11" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="N11" s="14">
-        <f>IF(L11&gt;0,M11/L11,0)</f>
-        <v/>
-      </c>
-      <c r="O11" s="15">
-        <f>IFERROR(INDEX(Policy!$B$12:$B$17,MATCH(C11,Policy!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="P11" s="8">
-        <f>IF(AND(I11="corporate",N11&gt;O11),"Yes","No")</f>
-        <v/>
-      </c>
-      <c r="Q11" s="8">
-        <f>IF(I11&lt;&gt;"corporate","None (not company money)",IF(AND(M11&lt;=Policy!$B$5,P11="No"),"Auto-approved","Manager"&amp;IF(OR(M11&gt;Policy!$B$6,P11="Yes")," → Dept head","")&amp;IF(AND(K11="Yes",OR(C11=Policy!$A$20,C11=Policy!$A$21))," → Compliance","")&amp;IF(M11&gt;Policy!$B$7," → Finance","")))</f>
-        <v/>
-      </c>
-      <c r="R11" s="8" t="inlineStr">
+      <c r="P11" s="11" t="n">
+        <v>7000</v>
+      </c>
+      <c r="Q11" s="13">
+        <f>IF(O11&gt;0,P11/O11,0)</f>
+        <v/>
+      </c>
+      <c r="R11" s="13">
+        <f>IFERROR(INDEX(Policy!$B$12:$B$18,MATCH(C11,Policy!$A$12:$A$18,0)),0)</f>
+        <v/>
+      </c>
+      <c r="S11" s="8">
+        <f>IF(AND(L11="corporate",Q11&gt;R11),"Yes","No")</f>
+        <v/>
+      </c>
+      <c r="T11" s="8">
+        <f>IF(L11&lt;&gt;"corporate","None (not company money)",IF(AND(P11&lt;=Policy!$B$5,S11="No"),"Auto-approved","Manager"&amp;IF(OR(P11&gt;Policy!$B$6,S11="Yes")," → Dept head","")&amp;IF(AND(N11="Yes",OR(C11=Policy!$A$21,C11=Policy!$A$22))," → Compliance","")&amp;IF(P11&gt;Policy!$B$7," → Finance","")))</f>
+        <v/>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="S11" s="8" t="inlineStr">
+      <c r="V11" s="8" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="T11" s="8" t="inlineStr"/>
+      <c r="W11" s="8" t="inlineStr"/>
+      <c r="X11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -2314,88 +4881,104 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Spa day wellbeing stipend, reimburse me, for 1 Oct 5</t>
+          <t>Cooking class on my wellbeing allowance, reimburse me, for 1 on 5 Oct</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>Napa Valley Wine Retreat</t>
+          <t>Cooking class on my wellbeing allowance, reimburse me, for 1 on 5 Oct</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Leo Martins</t>
+          <t>Hyderabad Cooking Studio</t>
         </is>
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>Telangana</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>Arjun Reddy</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
           <t>product</t>
         </is>
       </c>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="L12" s="12" t="inlineStr">
         <is>
           <t>reimbursable</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>wellbeing</t>
         </is>
       </c>
-      <c r="K12" s="12" t="inlineStr">
+      <c r="N12" s="12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="O12" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M12" s="13" t="n">
-        <v>450</v>
-      </c>
-      <c r="N12" s="14">
-        <f>IF(L12&gt;0,M12/L12,0)</f>
-        <v/>
-      </c>
-      <c r="O12" s="15">
-        <f>IFERROR(INDEX(Policy!$B$12:$B$17,MATCH(C12,Policy!$A$12:$A$17,0)),0)</f>
-        <v/>
-      </c>
-      <c r="P12" s="8">
-        <f>IF(AND(I12="corporate",N12&gt;O12),"Yes","No")</f>
-        <v/>
-      </c>
-      <c r="Q12" s="8">
-        <f>IF(I12&lt;&gt;"corporate","None (not company money)",IF(AND(M12&lt;=Policy!$B$5,P12="No"),"Auto-approved","Manager"&amp;IF(OR(M12&gt;Policy!$B$6,P12="Yes")," → Dept head","")&amp;IF(AND(K12="Yes",OR(C12=Policy!$A$20,C12=Policy!$A$21))," → Compliance","")&amp;IF(M12&gt;Policy!$B$7," → Finance","")))</f>
-        <v/>
-      </c>
-      <c r="R12" s="8" t="inlineStr">
+      <c r="P12" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="Q12" s="13">
+        <f>IF(O12&gt;0,P12/O12,0)</f>
+        <v/>
+      </c>
+      <c r="R12" s="13">
+        <f>IFERROR(INDEX(Policy!$B$12:$B$18,MATCH(C12,Policy!$A$12:$A$18,0)),0)</f>
+        <v/>
+      </c>
+      <c r="S12" s="8">
+        <f>IF(AND(L12="corporate",Q12&gt;R12),"Yes","No")</f>
+        <v/>
+      </c>
+      <c r="T12" s="8">
+        <f>IF(L12&lt;&gt;"corporate","None (not company money)",IF(AND(P12&lt;=Policy!$B$5,S12="No"),"Auto-approved","Manager"&amp;IF(OR(P12&gt;Policy!$B$6,S12="Yes")," → Dept head","")&amp;IF(AND(N12="Yes",OR(C12=Policy!$A$21,C12=Policy!$A$22))," → Compliance","")&amp;IF(P12&gt;Policy!$B$7," → Finance","")))</f>
+        <v/>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="S12" s="8" t="inlineStr">
+      <c r="V12" s="8" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
       </c>
-      <c r="T12" s="8" t="inlineStr"/>
+      <c r="W12" s="8" t="inlineStr"/>
+      <c r="X12" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Note: column Q applies the Policy sheet thresholds. Column R is what the agents recorded; it also skips self-approval (an approver who is the requester is replaced by their manager) and adds Finance when a department budget is exceeded.</t>
+          <t>Column T applies the Policy sheet. Column U is what the agents recorded; it also skips self-approval (the requester's own step moves to their manager and duplicates are dropped) and adds Finance when a department budget is exceeded.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="P2:P12">
+  <conditionalFormatting sqref="S2:S12">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Yes"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I2:I12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="L2:L12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"corporate,reimbursable,personal,shared"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2416,9 +4999,9 @@
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -2445,17 +5028,17 @@
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
-          <t>Quarterly budget ($)</t>
+          <t>Quarterly budget (₹)</t>
         </is>
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
-          <t>Committed ($)</t>
+          <t>Committed (₹)</t>
         </is>
       </c>
       <c r="G1" s="7" t="inlineStr">
         <is>
-          <t>Remaining ($)</t>
+          <t>Remaining (₹)</t>
         </is>
       </c>
       <c r="H1" s="7" t="inlineStr">
@@ -2482,21 +5065,21 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Elena Brooks</t>
+          <t>Priya Sharma</t>
         </is>
       </c>
       <c r="E2" s="9" t="n">
-        <v>60000</v>
-      </c>
-      <c r="F2" s="15">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$H$2:$H$12,A2,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$H$2:$H$12,A2,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$H$2:$H$12,A2,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="G2" s="15">
+        <v>6000000</v>
+      </c>
+      <c r="F2" s="13">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$K$2:$K$12,A2,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$K$2:$K$12,A2,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$K$2:$K$12,A2,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="G2" s="13">
         <f>E2-F2</f>
         <v/>
       </c>
-      <c r="H2" s="16">
+      <c r="H2" s="14">
         <f>IF(E2&gt;0,F2/E2,0)</f>
         <v/>
       </c>
@@ -2519,21 +5102,21 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Ana Ruiz</t>
+          <t>Kavya Nair</t>
         </is>
       </c>
       <c r="E3" s="9" t="n">
-        <v>25000</v>
-      </c>
-      <c r="F3" s="15">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$H$2:$H$12,A3,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$H$2:$H$12,A3,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$H$2:$H$12,A3,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="G3" s="15">
+        <v>2000000</v>
+      </c>
+      <c r="F3" s="13">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$K$2:$K$12,A3,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$K$2:$K$12,A3,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$K$2:$K$12,A3,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="G3" s="13">
         <f>E3-F3</f>
         <v/>
       </c>
-      <c r="H3" s="16">
+      <c r="H3" s="14">
         <f>IF(E3&gt;0,F3/E3,0)</f>
         <v/>
       </c>
@@ -2556,21 +5139,21 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Kim Nguyen</t>
+          <t>Neha Gupta</t>
         </is>
       </c>
       <c r="E4" s="9" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F4" s="15">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$H$2:$H$12,A4,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$H$2:$H$12,A4,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$H$2:$H$12,A4,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="G4" s="15">
+        <v>3000000</v>
+      </c>
+      <c r="F4" s="13">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$K$2:$K$12,A4,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$K$2:$K$12,A4,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$K$2:$K$12,A4,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="G4" s="13">
         <f>E4-F4</f>
         <v/>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="14">
         <f>IF(E4&gt;0,F4/E4,0)</f>
         <v/>
       </c>
@@ -2593,44 +5176,44 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Sam Okafor</t>
+          <t>Vikram Singh</t>
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F5" s="15">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$H$2:$H$12,A5,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$H$2:$H$12,A5,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$H$2:$H$12,A5,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="G5" s="15">
+        <v>1000000</v>
+      </c>
+      <c r="F5" s="13">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$K$2:$K$12,A5,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$K$2:$K$12,A5,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$K$2:$K$12,A5,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="G5" s="13">
         <f>E5-F5</f>
         <v/>
       </c>
-      <c r="H5" s="16">
+      <c r="H5" s="14">
         <f>IF(E5&gt;0,F5/E5,0)</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="16">
         <f>SUM(E2:E5)</f>
         <v/>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="16">
         <f>SUM(F2:F5)</f>
         <v/>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="16">
         <f>SUM(G2:G5)</f>
         <v/>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="17">
         <f>IF(E6&gt;0,F6/E6,0)</f>
         <v/>
       </c>
@@ -2661,7 +5244,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
@@ -2669,7 +5252,7 @@
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2700,7 +5283,7 @@
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
-          <t>Amount ($)</t>
+          <t>Amount (₹)</t>
         </is>
       </c>
       <c r="G1" s="7" t="inlineStr">
@@ -2710,32 +5293,32 @@
       </c>
       <c r="H1" s="7" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Ananya Iyer</t>
         </is>
       </c>
       <c r="I1" s="7" t="inlineStr">
         <is>
-          <t>Daniel Chen</t>
+          <t>Rohan Iyer</t>
         </is>
       </c>
       <c r="J1" s="7" t="inlineStr">
         <is>
-          <t>Lucy Chen</t>
+          <t>Diya Iyer</t>
         </is>
       </c>
       <c r="K1" s="7" t="inlineStr">
         <is>
-          <t>Leo Martins</t>
+          <t>Arjun Reddy</t>
         </is>
       </c>
       <c r="L1" s="7" t="inlineStr">
         <is>
-          <t>Priya Shah</t>
+          <t>Sneha Kapoor</t>
         </is>
       </c>
       <c r="M1" s="7" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Karthik Rao</t>
         </is>
       </c>
       <c r="N1" s="7" t="inlineStr">
@@ -2757,43 +5340,43 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Chen family</t>
+          <t>Iyer family</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Dinner with my family Saturday — split with the family</t>
+          <t>Kaveri Diaries · 2D · 3 tickets</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
-        </is>
-      </c>
-      <c r="F2" s="13" t="n">
-        <v>420</v>
+          <t>Ananya Iyer</t>
+        </is>
+      </c>
+      <c r="F2" s="18" t="n">
+        <v>660</v>
       </c>
       <c r="G2" s="8" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
-      <c r="H2" s="13" t="n">
-        <v>140</v>
-      </c>
-      <c r="I2" s="13" t="n">
-        <v>140</v>
-      </c>
-      <c r="J2" s="13" t="n">
-        <v>140</v>
-      </c>
-      <c r="K2" s="13" t="n">
+      <c r="H2" s="18" t="n">
+        <v>220</v>
+      </c>
+      <c r="I2" s="18" t="n">
+        <v>220</v>
+      </c>
+      <c r="J2" s="18" t="n">
+        <v>220</v>
+      </c>
+      <c r="K2" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L2" s="13" t="n">
+      <c r="L2" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M2" s="13" t="n">
+      <c r="M2" s="18" t="n">
         <v>0</v>
       </c>
       <c r="N2" s="8">
@@ -2809,49 +5392,49 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Weekend crew</t>
+          <t>Weekend gang</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Giants game tickets with friends for 4 Sunday, split</t>
+          <t>Stand-up Saturday · 4 × Regular</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>Leo Martins</t>
-        </is>
-      </c>
-      <c r="F3" s="13" t="n">
-        <v>720</v>
+          <t>Arjun Reddy</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="n">
+        <v>2000</v>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
-      <c r="H3" s="13" t="n">
-        <v>180</v>
-      </c>
-      <c r="I3" s="13" t="n">
+      <c r="H3" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="I3" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J3" s="13" t="n">
+      <c r="J3" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K3" s="13" t="n">
-        <v>180</v>
-      </c>
-      <c r="L3" s="13" t="n">
-        <v>180</v>
-      </c>
-      <c r="M3" s="13" t="n">
-        <v>180</v>
+      <c r="K3" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="L3" s="18" t="n">
+        <v>500</v>
+      </c>
+      <c r="M3" s="18" t="n">
+        <v>500</v>
       </c>
       <c r="N3" s="8">
         <f>IF(ROUND(SUM(H3:M3)-F3,2)=0,"OK","Mismatch")</f>
@@ -2866,49 +5449,49 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Weekend crew</t>
+          <t>Weekend gang</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Uber to the ballpark</t>
+          <t>Cabs to the venue</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>Priya Shah</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="n">
-        <v>96</v>
+          <t>Sneha Kapoor</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>640</v>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
           <t>equal</t>
         </is>
       </c>
-      <c r="H4" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="I4" s="13" t="n">
+      <c r="H4" s="18" t="n">
+        <v>160</v>
+      </c>
+      <c r="I4" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="13" t="n">
+      <c r="J4" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="L4" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="M4" s="13" t="n">
-        <v>24</v>
+      <c r="K4" s="18" t="n">
+        <v>160</v>
+      </c>
+      <c r="L4" s="18" t="n">
+        <v>160</v>
+      </c>
+      <c r="M4" s="18" t="n">
+        <v>160</v>
       </c>
       <c r="N4" s="8">
         <f>IF(ROUND(SUM(H4:M4)-F4,2)=0,"OK","Mismatch")</f>
@@ -2923,48 +5506,48 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>Chen family</t>
+          <t>Iyer family</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Groceries for the family BBQ</t>
+          <t>Groceries for the Onam sadya</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>Daniel Chen</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>180</v>
+          <t>Rohan Iyer</t>
+        </is>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>4800</v>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
           <t>shares</t>
         </is>
       </c>
-      <c r="H5" s="13" t="n">
-        <v>45</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>45</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>90</v>
-      </c>
-      <c r="K5" s="13" t="n">
+      <c r="H5" s="18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="I5" s="18" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>2400</v>
+      </c>
+      <c r="K5" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="L5" s="13" t="n">
+      <c r="L5" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M5" s="13" t="n">
+      <c r="M5" s="18" t="n">
         <v>0</v>
       </c>
       <c r="N5" s="8">
@@ -2975,14 +5558,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Shares are computed by the Split agent in whole cents so each row adds up exactly (Check column).</t>
+          <t>Shares are computed by the Split agent in whole paise, so each row adds up exactly (Check column).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Settlements</t>
+          <t>Settlements (UPI payments recorded)</t>
         </is>
       </c>
     </row>
@@ -3009,7 +5592,7 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>Amount ($)</t>
+          <t>Amount (₹)</t>
         </is>
       </c>
     </row>
@@ -3021,21 +5604,21 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Weekend crew</t>
+          <t>Weekend gang</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Karthik Rao</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Leo Martins</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>40</v>
+          <t>Arjun Reddy</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -3054,10 +5637,10 @@
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
@@ -3075,27 +5658,27 @@
       </c>
       <c r="C1" s="7" t="inlineStr">
         <is>
-          <t>Paid ($)</t>
+          <t>Paid (₹)</t>
         </is>
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
-          <t>Share ($)</t>
+          <t>Share (₹)</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
-          <t>Settlements sent ($)</t>
+          <t>Settlements sent (₹)</t>
         </is>
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
-          <t>Settlements received ($)</t>
+          <t>Settlements received (₹)</t>
         </is>
       </c>
       <c r="G1" s="7" t="inlineStr">
         <is>
-          <t>Net balance ($)</t>
+          <t>Net balance (₹)</t>
         </is>
       </c>
       <c r="H1" s="7" t="inlineStr">
@@ -3107,31 +5690,31 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Chen family</t>
+          <t>Iyer family</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
-        </is>
-      </c>
-      <c r="C2" s="14">
+          <t>Ananya Iyer</t>
+        </is>
+      </c>
+      <c r="C2" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$C$2:$C$5,A2,'Group Ledger'!$E$2:$E$5,B2)</f>
         <v/>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="19">
         <f>SUMIFS('Group Ledger'!$H$2:$H$5,'Group Ledger'!$C$2:$C$5,A2)</f>
         <v/>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="19">
         <f>SUMIFS('Group Ledger'!$E$11:$E$11,'Group Ledger'!$B$11:$B$11,A2,'Group Ledger'!$C$11:$C$11,B2)</f>
         <v/>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="19">
         <f>SUMIFS('Group Ledger'!$E$11:$E$11,'Group Ledger'!$B$11:$B$11,A2,'Group Ledger'!$D$11:$D$11,B2)</f>
         <v/>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="19">
         <f>C2-D2+E2-F2</f>
         <v/>
       </c>
@@ -3143,31 +5726,31 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Chen family</t>
+          <t>Iyer family</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Daniel Chen</t>
-        </is>
-      </c>
-      <c r="C3" s="14">
+          <t>Rohan Iyer</t>
+        </is>
+      </c>
+      <c r="C3" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$C$2:$C$5,A3,'Group Ledger'!$E$2:$E$5,B3)</f>
         <v/>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="19">
         <f>SUMIFS('Group Ledger'!$I$2:$I$5,'Group Ledger'!$C$2:$C$5,A3)</f>
         <v/>
       </c>
-      <c r="E3" s="14">
+      <c r="E3" s="19">
         <f>SUMIFS('Group Ledger'!$E$11:$E$11,'Group Ledger'!$B$11:$B$11,A3,'Group Ledger'!$C$11:$C$11,B3)</f>
         <v/>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="19">
         <f>SUMIFS('Group Ledger'!$E$11:$E$11,'Group Ledger'!$B$11:$B$11,A3,'Group Ledger'!$D$11:$D$11,B3)</f>
         <v/>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="19">
         <f>C3-D3+E3-F3</f>
         <v/>
       </c>
@@ -3179,31 +5762,31 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>Chen family</t>
+          <t>Iyer family</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Lucy Chen</t>
-        </is>
-      </c>
-      <c r="C4" s="14">
+          <t>Diya Iyer</t>
+        </is>
+      </c>
+      <c r="C4" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$C$2:$C$5,A4,'Group Ledger'!$E$2:$E$5,B4)</f>
         <v/>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="19">
         <f>SUMIFS('Group Ledger'!$J$2:$J$5,'Group Ledger'!$C$2:$C$5,A4)</f>
         <v/>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="19">
         <f>SUMIFS('Group Ledger'!$E$11:$E$11,'Group Ledger'!$B$11:$B$11,A4,'Group Ledger'!$C$11:$C$11,B4)</f>
         <v/>
       </c>
-      <c r="F4" s="14">
+      <c r="F4" s="19">
         <f>SUMIFS('Group Ledger'!$E$11:$E$11,'Group Ledger'!$B$11:$B$11,A4,'Group Ledger'!$D$11:$D$11,B4)</f>
         <v/>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="19">
         <f>C4-D4+E4-F4</f>
         <v/>
       </c>
@@ -3215,31 +5798,31 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Weekend crew</t>
+          <t>Weekend gang</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
-        </is>
-      </c>
-      <c r="C5" s="14">
+          <t>Ananya Iyer</t>
+        </is>
+      </c>
+      <c r="C5" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$C$2:$C$5,A5,'Group Ledger'!$E$2:$E$5,B5)</f>
         <v/>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="19">
         <f>SUMIFS('Group Ledger'!$H$2:$H$5,'Group Ledger'!$C$2:$C$5,A5)</f>
         <v/>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="19">
         <f>SUMIFS('Group Ledger'!$E$11:$E$11,'Group Ledger'!$B$11:$B$11,A5,'Group Ledger'!$C$11:$C$11,B5)</f>
         <v/>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="19">
         <f>SUMIFS('Group Ledger'!$E$11:$E$11,'Group Ledger'!$B$11:$B$11,A5,'Group Ledger'!$D$11:$D$11,B5)</f>
         <v/>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="19">
         <f>C5-D5+E5-F5</f>
         <v/>
       </c>
@@ -3251,31 +5834,31 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Weekend crew</t>
+          <t>Weekend gang</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Leo Martins</t>
-        </is>
-      </c>
-      <c r="C6" s="14">
+          <t>Arjun Reddy</t>
+        </is>
+      </c>
+      <c r="C6" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$C$2:$C$5,A6,'Group Ledger'!$E$2:$E$5,B6)</f>
         <v/>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="19">
         <f>SUMIFS('Group Ledger'!$K$2:$K$5,'Group Ledger'!$C$2:$C$5,A6)</f>
         <v/>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="19">
         <f>SUMIFS('Group Ledger'!$E$11:$E$11,'Group Ledger'!$B$11:$B$11,A6,'Group Ledger'!$C$11:$C$11,B6)</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="19">
         <f>SUMIFS('Group Ledger'!$E$11:$E$11,'Group Ledger'!$B$11:$B$11,A6,'Group Ledger'!$D$11:$D$11,B6)</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="19">
         <f>C6-D6+E6-F6</f>
         <v/>
       </c>
@@ -3287,31 +5870,31 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Weekend crew</t>
+          <t>Weekend gang</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Priya Shah</t>
-        </is>
-      </c>
-      <c r="C7" s="14">
+          <t>Sneha Kapoor</t>
+        </is>
+      </c>
+      <c r="C7" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$C$2:$C$5,A7,'Group Ledger'!$E$2:$E$5,B7)</f>
         <v/>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="19">
         <f>SUMIFS('Group Ledger'!$L$2:$L$5,'Group Ledger'!$C$2:$C$5,A7)</f>
         <v/>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="19">
         <f>SUMIFS('Group Ledger'!$E$11:$E$11,'Group Ledger'!$B$11:$B$11,A7,'Group Ledger'!$C$11:$C$11,B7)</f>
         <v/>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="19">
         <f>SUMIFS('Group Ledger'!$E$11:$E$11,'Group Ledger'!$B$11:$B$11,A7,'Group Ledger'!$D$11:$D$11,B7)</f>
         <v/>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="19">
         <f>C7-D7+E7-F7</f>
         <v/>
       </c>
@@ -3323,31 +5906,31 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Weekend crew</t>
+          <t>Weekend gang</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
-        </is>
-      </c>
-      <c r="C8" s="14">
+          <t>Karthik Rao</t>
+        </is>
+      </c>
+      <c r="C8" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$C$2:$C$5,A8,'Group Ledger'!$E$2:$E$5,B8)</f>
         <v/>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="19">
         <f>SUMIFS('Group Ledger'!$M$2:$M$5,'Group Ledger'!$C$2:$C$5,A8)</f>
         <v/>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="19">
         <f>SUMIFS('Group Ledger'!$E$11:$E$11,'Group Ledger'!$B$11:$B$11,A8,'Group Ledger'!$C$11:$C$11,B8)</f>
         <v/>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="19">
         <f>SUMIFS('Group Ledger'!$E$11:$E$11,'Group Ledger'!$B$11:$B$11,A8,'Group Ledger'!$D$11:$D$11,B8)</f>
         <v/>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="19">
         <f>C8-D8+E8-F8</f>
         <v/>
       </c>
@@ -3359,7 +5942,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Net balance = paid − own share + settlements sent − settlements received. Positive: is owed money. Negative: owes money. Each group sums to zero.</t>
+          <t>Positive: is owed money. Negative: owes money. Each group sums to zero.</t>
         </is>
       </c>
     </row>
@@ -3378,14 +5961,14 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -3407,44 +5990,44 @@
       </c>
       <c r="D1" s="7" t="inlineStr">
         <is>
-          <t>Company-paid ($)</t>
+          <t>Company-paid (₹)</t>
         </is>
       </c>
       <c r="E1" s="7" t="inlineStr">
         <is>
-          <t>Reimbursable ($)</t>
+          <t>Reimbursable (₹)</t>
         </is>
       </c>
       <c r="F1" s="7" t="inlineStr">
         <is>
-          <t>Personal ($)</t>
+          <t>Personal (₹)</t>
         </is>
       </c>
       <c r="G1" s="7" t="inlineStr">
         <is>
-          <t>Paid for groups ($)</t>
+          <t>Paid for groups (₹)</t>
         </is>
       </c>
       <c r="H1" s="7" t="inlineStr">
         <is>
-          <t>Own group share ($)</t>
+          <t>Own group share (₹)</t>
         </is>
       </c>
       <c r="I1" s="7" t="inlineStr">
         <is>
-          <t>Out of pocket ($)</t>
+          <t>Out of pocket (₹)</t>
         </is>
       </c>
       <c r="J1" s="7" t="inlineStr">
         <is>
-          <t>Total influenced ($)</t>
+          <t>Total handled (₹)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Ananya Iyer</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
@@ -3457,31 +6040,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="D2" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A2,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A2,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A2,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="E2" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A2,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A2,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A2,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="F2" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A2,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A2,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A2,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="G2" s="14">
+      <c r="D2" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A2,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A2,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A2,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="E2" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A2,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A2,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A2,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="F2" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A2,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A2,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A2,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="G2" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$E$2:$E$5,A2)</f>
         <v/>
       </c>
-      <c r="H2" s="14">
+      <c r="H2" s="19">
         <f>SUM('Group Ledger'!H2:H5)</f>
         <v/>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="19">
         <f>E2+F2+H2</f>
         <v/>
       </c>
-      <c r="J2" s="14">
+      <c r="J2" s="19">
         <f>D2+E2+F2+G2</f>
         <v/>
       </c>
@@ -3489,7 +6072,7 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Raj Patel</t>
+          <t>Rahul Mehta</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -3502,30 +6085,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="D3" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A3,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A3,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A3,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="E3" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A3,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A3,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A3,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="F3" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A3,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A3,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A3,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="G3" s="14">
+      <c r="D3" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A3,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A3,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A3,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="E3" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A3,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A3,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A3,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="F3" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A3,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A3,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A3,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="G3" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$E$2:$E$5,A3)</f>
         <v/>
       </c>
-      <c r="H3" s="14" t="n">
+      <c r="H3" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="19">
         <f>E3+F3+H3</f>
         <v/>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="19">
         <f>D3+E3+F3+G3</f>
         <v/>
       </c>
@@ -3533,7 +6116,7 @@
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>Elena Brooks</t>
+          <t>Priya Sharma</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -3546,30 +6129,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="D4" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A4,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A4,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A4,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="E4" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A4,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A4,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A4,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="F4" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A4,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A4,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A4,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="G4" s="14">
+      <c r="D4" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A4,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A4,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A4,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="E4" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A4,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A4,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A4,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="F4" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A4,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A4,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A4,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="G4" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$E$2:$E$5,A4)</f>
         <v/>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="H4" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="19">
         <f>E4+F4+H4</f>
         <v/>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="19">
         <f>D4+E4+F4+G4</f>
         <v/>
       </c>
@@ -3577,7 +6160,7 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Leo Martins</t>
+          <t>Arjun Reddy</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -3590,31 +6173,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="D5" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A5,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A5,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A5,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="E5" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A5,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A5,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A5,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="F5" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A5,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A5,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A5,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="G5" s="14">
+      <c r="D5" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A5,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A5,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A5,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="E5" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A5,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A5,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A5,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="F5" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A5,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A5,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A5,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="G5" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$E$2:$E$5,A5)</f>
         <v/>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="19">
         <f>SUM('Group Ledger'!K2:K5)</f>
         <v/>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="19">
         <f>E5+F5+H5</f>
         <v/>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="19">
         <f>D5+E5+F5+G5</f>
         <v/>
       </c>
@@ -3622,7 +6205,7 @@
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Ana Ruiz</t>
+          <t>Kavya Nair</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -3635,30 +6218,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="D6" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A6,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A6,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A6,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="E6" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A6,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A6,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A6,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="F6" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A6,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A6,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A6,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="G6" s="14">
+      <c r="D6" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A6,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A6,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A6,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="E6" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A6,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A6,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A6,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="F6" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A6,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A6,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A6,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="G6" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$E$2:$E$5,A6)</f>
         <v/>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="19">
         <f>E6+F6+H6</f>
         <v/>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="19">
         <f>D6+E6+F6+G6</f>
         <v/>
       </c>
@@ -3666,7 +6249,7 @@
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Sam Okafor</t>
+          <t>Vikram Singh</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -3679,30 +6262,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="D7" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A7,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A7,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A7,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="E7" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A7,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A7,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A7,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="F7" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A7,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A7,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A7,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="G7" s="14">
+      <c r="D7" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A7,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A7,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A7,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="E7" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A7,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A7,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A7,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="F7" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A7,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A7,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A7,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="G7" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$E$2:$E$5,A7)</f>
         <v/>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="19">
         <f>E7+F7+H7</f>
         <v/>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="19">
         <f>D7+E7+F7+G7</f>
         <v/>
       </c>
@@ -3710,7 +6293,7 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Kim Nguyen</t>
+          <t>Neha Gupta</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -3723,30 +6306,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="D8" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A8,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A8,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A8,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="E8" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A8,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A8,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A8,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="F8" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A8,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A8,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A8,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="G8" s="14">
+      <c r="D8" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A8,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A8,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A8,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="E8" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A8,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A8,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A8,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="F8" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A8,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A8,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A8,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="G8" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$E$2:$E$5,A8)</f>
         <v/>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H8" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="19">
         <f>E8+F8+H8</f>
         <v/>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="19">
         <f>D8+E8+F8+G8</f>
         <v/>
       </c>
@@ -3754,7 +6337,7 @@
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Omar Haddad</t>
+          <t>Farhan Qureshi</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -3767,30 +6350,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="D9" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A9,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A9,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A9,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="E9" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A9,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A9,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A9,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="F9" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A9,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A9,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A9,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="G9" s="14">
+      <c r="D9" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A9,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A9,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A9,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="E9" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A9,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A9,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A9,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="F9" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A9,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A9,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A9,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="G9" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$E$2:$E$5,A9)</f>
         <v/>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="19">
         <f>E9+F9+H9</f>
         <v/>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="19">
         <f>D9+E9+F9+G9</f>
         <v/>
       </c>
@@ -3798,7 +6381,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Ivy Walsh</t>
+          <t>Meera Joshi</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -3811,30 +6394,30 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="D10" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A10,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A10,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A10,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="E10" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A10,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A10,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A10,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="F10" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A10,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A10,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A10,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="G10" s="14">
+      <c r="D10" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A10,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A10,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A10,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="E10" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A10,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A10,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A10,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="F10" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A10,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A10,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A10,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="G10" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$E$2:$E$5,A10)</f>
         <v/>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="19">
         <f>E10+F10+H10</f>
         <v/>
       </c>
-      <c r="J10" s="14">
+      <c r="J10" s="19">
         <f>D10+E10+F10+G10</f>
         <v/>
       </c>
@@ -3842,12 +6425,12 @@
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Daniel Chen</t>
+          <t>Rohan Iyer</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Family (Maya's partner)</t>
+          <t>Family (Ananya’s husband)</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -3855,31 +6438,31 @@
           <t>Guest</t>
         </is>
       </c>
-      <c r="D11" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A11,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A11,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A11,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="E11" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A11,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A11,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A11,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="F11" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A11,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A11,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A11,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="G11" s="14">
+      <c r="D11" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A11,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A11,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A11,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="E11" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A11,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A11,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A11,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="F11" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A11,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A11,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A11,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="G11" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$E$2:$E$5,A11)</f>
         <v/>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="19">
         <f>SUM('Group Ledger'!I2:I5)</f>
         <v/>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="19">
         <f>E11+F11+H11</f>
         <v/>
       </c>
-      <c r="J11" s="14">
+      <c r="J11" s="19">
         <f>D11+E11+F11+G11</f>
         <v/>
       </c>
@@ -3887,12 +6470,12 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Lucy Chen</t>
+          <t>Diya Iyer</t>
         </is>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Family (Maya's sister)</t>
+          <t>Family (Ananya’s sister)</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -3900,31 +6483,31 @@
           <t>Guest</t>
         </is>
       </c>
-      <c r="D12" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A12,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A12,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A12,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="E12" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A12,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A12,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A12,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="F12" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A12,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A12,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A12,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="G12" s="14">
+      <c r="D12" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A12,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A12,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A12,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="E12" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A12,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A12,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A12,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="F12" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A12,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A12,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A12,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="G12" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$E$2:$E$5,A12)</f>
         <v/>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="19">
         <f>SUM('Group Ledger'!J2:J5)</f>
         <v/>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="19">
         <f>E12+F12+H12</f>
         <v/>
       </c>
-      <c r="J12" s="14">
+      <c r="J12" s="19">
         <f>D12+E12+F12+G12</f>
         <v/>
       </c>
@@ -3932,7 +6515,7 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Priya Shah</t>
+          <t>Sneha Kapoor</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
@@ -3945,31 +6528,31 @@
           <t>Guest</t>
         </is>
       </c>
-      <c r="D13" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A13,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A13,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A13,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="E13" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A13,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A13,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A13,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="F13" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A13,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A13,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A13,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="G13" s="14">
+      <c r="D13" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A13,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A13,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A13,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="E13" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A13,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A13,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A13,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="F13" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A13,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A13,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A13,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="G13" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$E$2:$E$5,A13)</f>
         <v/>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="19">
         <f>SUM('Group Ledger'!L2:L5)</f>
         <v/>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="19">
         <f>E13+F13+H13</f>
         <v/>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="19">
         <f>D13+E13+F13+G13</f>
         <v/>
       </c>
@@ -3977,7 +6560,7 @@
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Tom Becker</t>
+          <t>Karthik Rao</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -3990,37 +6573,37 @@
           <t>Guest</t>
         </is>
       </c>
-      <c r="D14" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A14,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A14,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A14,Bookings!$I$2:$I$12,"corporate",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="E14" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A14,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A14,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A14,Bookings!$I$2:$I$12,"reimbursable",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="F14" s="14">
-        <f>SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A14,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"pending_approval") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A14,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"approved") + SUMIFS(Bookings!$M$2:$M$12,Bookings!$G$2:$G$12,$A14,Bookings!$I$2:$I$12,"personal",Bookings!$S$2:$S$12,"confirmed")</f>
-        <v/>
-      </c>
-      <c r="G14" s="14">
+      <c r="D14" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A14,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A14,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A14,Bookings!$L$2:$L$12,"corporate",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="E14" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A14,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A14,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A14,Bookings!$L$2:$L$12,"reimbursable",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="F14" s="19">
+        <f>SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A14,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"pending_approval") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A14,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"approved") + SUMIFS(Bookings!$P$2:$P$12,Bookings!$J$2:$J$12,$A14,Bookings!$L$2:$L$12,"personal",Bookings!$V$2:$V$12,"confirmed")</f>
+        <v/>
+      </c>
+      <c r="G14" s="19">
         <f>SUMIFS('Group Ledger'!$F$2:$F$5,'Group Ledger'!$E$2:$E$5,A14)</f>
         <v/>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="19">
         <f>SUM('Group Ledger'!M2:M5)</f>
         <v/>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="19">
         <f>E14+F14+H14</f>
         <v/>
       </c>
-      <c r="J14" s="14">
+      <c r="J14" s="19">
         <f>D14+E14+F14+G14</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -4077,15 +6660,15 @@
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4121,12 +6704,12 @@
       </c>
       <c r="G1" s="7" t="inlineStr">
         <is>
-          <t>Total ($)</t>
+          <t>Total (₹)</t>
         </is>
       </c>
       <c r="H1" s="7" t="inlineStr">
         <is>
-          <t>Claimable ($)</t>
+          <t>Claimable (₹)</t>
         </is>
       </c>
       <c r="I1" s="7" t="inlineStr">
@@ -4153,12 +6736,12 @@
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Leo Martins</t>
+          <t>Arjun Reddy</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Lifestyle &amp; wellbeing stipend</t>
+          <t>Lifestyle &amp; wellbeing allowance</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
@@ -4174,15 +6757,15 @@
           <t>BK-1011</t>
         </is>
       </c>
-      <c r="G2" s="13" t="n">
-        <v>450</v>
-      </c>
-      <c r="H2" s="13" t="n">
-        <v>450</v>
+      <c r="G2" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H2" s="11" t="n">
+        <v>3000</v>
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
-          <t>Benefits team (Omar Haddad: approved)</t>
+          <t>Benefits team (Farhan Qureshi: approved)</t>
         </is>
       </c>
       <c r="J2" s="8" t="inlineStr">
@@ -4192,7 +6775,7 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22T23:38:16.783Z</t>
+          <t>2026-09-23T00:00:35.488Z</t>
         </is>
       </c>
     </row>
@@ -4204,7 +6787,7 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Maya Chen</t>
+          <t>Ananya Iyer</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -4225,15 +6808,15 @@
           <t>BK-1010</t>
         </is>
       </c>
-      <c r="G3" s="13" t="n">
-        <v>280</v>
-      </c>
-      <c r="H3" s="13" t="n">
-        <v>280</v>
+      <c r="G3" s="11" t="n">
+        <v>7000</v>
+      </c>
+      <c r="H3" s="11" t="n">
+        <v>7000</v>
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>Manager (Raj Patel: approved) → Finance team (Sam Okafor: pending)</t>
+          <t>Manager (Rahul Mehta: approved) → Finance team (Vikram Singh: pending)</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
@@ -4243,7 +6826,7 @@
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>2026-09-22T23:38:16.783Z</t>
+          <t>2026-09-23T00:00:35.488Z</t>
         </is>
       </c>
     </row>
@@ -4281,12 +6864,12 @@
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Lifestyle &amp; wellbeing stipend</t>
+          <t>Lifestyle &amp; wellbeing allowance</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Benefits (capped at stipend balance)</t>
+          <t>Benefits (capped at the allowance balance)</t>
         </is>
       </c>
     </row>
@@ -4304,9 +6887,9 @@
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4319,22 +6902,22 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Enter the amount and method (yellow). Weights: exact $, percent, or share units. 'equal' ignores weights.</t>
+          <t>Enter the amount and method (yellow). Weights: exact ₹, percent, or share units. 'equal' ignores weights.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>Amount ($)</t>
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Amount (₹)</t>
         </is>
       </c>
       <c r="B4" s="21" t="n">
-        <v>300</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
@@ -4358,20 +6941,20 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Share ($)</t>
+          <t>Share (₹)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>Maya</t>
+          <t>Ananya</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="19">
         <f>IF($B$5="equal",IF(COUNTA($A$8:$A$11)&gt;0,$B$4/COUNTA($A$8:$A$11),0),IF($B$5="exact",B8,IF($B$5="percent",$B$4*B8/100,IF(SUM($B$8:$B$11)&gt;0,$B$4*B8/SUM($B$8:$B$11),0))))</f>
         <v/>
       </c>
@@ -4379,13 +6962,13 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Rohan</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="19">
         <f>IF($B$5="equal",IF(COUNTA($A$8:$A$11)&gt;0,$B$4/COUNTA($A$8:$A$11),0),IF($B$5="exact",B9,IF($B$5="percent",$B$4*B9/100,IF(SUM($B$8:$B$11)&gt;0,$B$4*B9/SUM($B$8:$B$11),0))))</f>
         <v/>
       </c>
@@ -4393,13 +6976,13 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Lucy</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="B10" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="19">
         <f>IF($B$5="equal",IF(COUNTA($A$8:$A$11)&gt;0,$B$4/COUNTA($A$8:$A$11),0),IF($B$5="exact",B10,IF($B$5="percent",$B$4*B10/100,IF(SUM($B$8:$B$11)&gt;0,$B$4*B10/SUM($B$8:$B$11),0))))</f>
         <v/>
       </c>
@@ -4413,13 +6996,13 @@
       <c r="B11" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="19">
         <f>IF($B$5="equal",IF(COUNTA($A$8:$A$11)&gt;0,$B$4/COUNTA($A$8:$A$11),0),IF($B$5="exact",B11,IF($B$5="percent",$B$4*B11/100,IF(SUM($B$8:$B$11)&gt;0,$B$4*B11/SUM($B$8:$B$11),0))))</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>Total of shares</t>
         </is>
@@ -4430,12 +7013,12 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="15">
         <f>IF(ROUND(C12-B4,2)=0,"Adds up","Does not add up")</f>
         <v/>
       </c>
@@ -4443,7 +7026,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Example: $300 with shares 2:1:1:0 → $150 / $75 / $75 / $0. The app rounds to cents and hands leftover cents to the largest weights.</t>
+          <t>Example: ₹3,000 with shares 2:1:1:0 → ₹1,500 / ₹750 / ₹750 / ₹0. The app rounds to the paisa and gives leftover paise to the largest weights.</t>
         </is>
       </c>
     </row>

--- a/entertainment-os/docs/Entertainment-OS-Workbook.xlsx
+++ b/entertainment-os/docs/Entertainment-OS-Workbook.xlsx
@@ -18,7 +18,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Split Calculator" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locations" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalog" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flow" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Sources" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flow" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -530,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -540,7 +541,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Entertainment OS — Operations Workbook (India)</t>
+          <t>Entertainment OS — Operations Workbook (India &amp; Canada)</t>
         </is>
       </c>
     </row>
@@ -679,65 +680,77 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Films now showing, their languages and formats, and the event types listed near you.</t>
+          <t>Sample films, their languages and formats, and the event types listed near you (live data replaces the samples when online).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>Data Sources</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>The free public APIs the app uses for live data, what each provides, and the fallbacks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>Flow</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Step-by-step flow of a request through the agents.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr"/>
-      <c r="B16" s="4" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Blue text</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Hard-coded input — safe to edit.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Yellow fill</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Key assumption / cell you are expected to change.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Black text</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Formula — do not overwrite.</t>
         </is>
@@ -754,7 +767,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C114"/>
+  <dimension ref="A1:C149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2482,194 +2495,789 @@
     <row r="102">
       <c r="A102" s="8" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Alberta</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Calgary</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Alberta</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Abu Dhabi</t>
+          <t>Edmonton</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="8" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Alberta</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Banff</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="8" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>Alberta</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Red Deer</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="8" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>England</t>
+          <t>British Columbia</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Manchester</t>
+          <t>Vancouver</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="8" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>British Columbia</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Edinburgh</t>
+          <t>Victoria</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="8" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>British Columbia</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>San Francisco</t>
+          <t>Surrey</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="8" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B109" s="8" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>British Columbia</t>
         </is>
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Los Angeles</t>
+          <t>Kelowna</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="8" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>British Columbia</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>New York City</t>
+          <t>Whistler</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="8" t="inlineStr">
         <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C111" s="8" t="inlineStr">
+        <is>
+          <t>Winnipeg</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t>Manitoba</t>
+        </is>
+      </c>
+      <c r="C112" s="8" t="inlineStr">
+        <is>
+          <t>Brandon</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>New Brunswick</t>
+        </is>
+      </c>
+      <c r="C113" s="8" t="inlineStr">
+        <is>
+          <t>Moncton</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B114" s="8" t="inlineStr">
+        <is>
+          <t>New Brunswick</t>
+        </is>
+      </c>
+      <c r="C114" s="8" t="inlineStr">
+        <is>
+          <t>Saint John</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B115" s="8" t="inlineStr">
+        <is>
+          <t>New Brunswick</t>
+        </is>
+      </c>
+      <c r="C115" s="8" t="inlineStr">
+        <is>
+          <t>Fredericton</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B116" s="8" t="inlineStr">
+        <is>
+          <t>Newfoundland and Labrador</t>
+        </is>
+      </c>
+      <c r="C116" s="8" t="inlineStr">
+        <is>
+          <t>St. John's</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B117" s="8" t="inlineStr">
+        <is>
+          <t>Nova Scotia</t>
+        </is>
+      </c>
+      <c r="C117" s="8" t="inlineStr">
+        <is>
+          <t>Halifax</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B118" s="8" t="inlineStr">
+        <is>
+          <t>Nova Scotia</t>
+        </is>
+      </c>
+      <c r="C118" s="8" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B119" s="8" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C119" s="8" t="inlineStr">
+        <is>
+          <t>Toronto</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B120" s="8" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C120" s="8" t="inlineStr">
+        <is>
+          <t>Ottawa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B121" s="8" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>Mississauga</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>Brampton</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B123" s="8" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>Hamilton</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B124" s="8" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>Waterloo</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B126" s="8" t="inlineStr">
+        <is>
+          <t>Ontario</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="inlineStr">
+        <is>
+          <t>Niagara Falls</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B127" s="8" t="inlineStr">
+        <is>
+          <t>Prince Edward Island</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>Charlottetown</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B128" s="8" t="inlineStr">
+        <is>
+          <t>Quebec</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t>Montreal</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B129" s="8" t="inlineStr">
+        <is>
+          <t>Quebec</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>Quebec City</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B130" s="8" t="inlineStr">
+        <is>
+          <t>Quebec</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t>Gatineau</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B131" s="8" t="inlineStr">
+        <is>
+          <t>Quebec</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>Laval</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B132" s="8" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t>Saskatoon</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>Saskatchewan</t>
+        </is>
+      </c>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>Regina</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B134" s="8" t="inlineStr">
+        <is>
+          <t>Northwest Territories</t>
+        </is>
+      </c>
+      <c r="C134" s="8" t="inlineStr">
+        <is>
+          <t>Yellowknife</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="inlineStr">
+        <is>
+          <t>Nunavut</t>
+        </is>
+      </c>
+      <c r="C135" s="8" t="inlineStr">
+        <is>
+          <t>Iqaluit</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="8" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t>Yukon</t>
+        </is>
+      </c>
+      <c r="C136" s="8" t="inlineStr">
+        <is>
+          <t>Whitehorse</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="8" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B137" s="8" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+      <c r="C137" s="8" t="inlineStr">
+        <is>
+          <t>Dubai</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="8" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="B138" s="8" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+      <c r="C138" s="8" t="inlineStr">
+        <is>
+          <t>Abu Dhabi</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="8" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B139" s="8" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C139" s="8" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B140" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C140" s="8" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B141" s="8" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="C141" s="8" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="8" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="B142" s="8" t="inlineStr">
+        <is>
+          <t>Scotland</t>
+        </is>
+      </c>
+      <c r="C142" s="8" t="inlineStr">
+        <is>
+          <t>Edinburgh</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="8" t="inlineStr">
+        <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="B111" s="8" t="inlineStr">
+      <c r="B143" s="8" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="C143" s="8" t="inlineStr">
+        <is>
+          <t>San Francisco</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B144" s="8" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="C144" s="8" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="C145" s="8" t="inlineStr">
+        <is>
+          <t>New York City</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="8" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="inlineStr">
         <is>
           <t>Texas</t>
         </is>
       </c>
-      <c r="C111" s="8" t="inlineStr">
+      <c r="C146" s="8" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="15" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="15" t="inlineStr">
         <is>
           <t>Other…</t>
         </is>
       </c>
-      <c r="B112" s="15" t="inlineStr">
+      <c r="B147" s="15" t="inlineStr">
         <is>
           <t>Other… (type any state or region)</t>
         </is>
       </c>
-      <c r="C112" s="15" t="inlineStr">
+      <c r="C147" s="15" t="inlineStr">
         <is>
           <t>Other… (type any city)</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
-        <is>
-          <t>36 Indian states &amp; union territories, 100 Indian cities, plus 4 other countries. Every level has an 'Other' option for typing a place that isn't listed.</t>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>36 Indian states &amp; union territories, 100 Indian cities, plus 5 other countries. Every level has an 'Other' option for typing a place that isn't listed.</t>
         </is>
       </c>
     </row>
@@ -2684,7 +3292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3062,8 +3670,20 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>Films, cinemas, events and venues are fictional demo data, generated for whichever city is selected.</t>
         </is>
@@ -3080,7 +3700,332 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Free source</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Key needed?</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Cache</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Used for</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="inlineStr">
+        <is>
+          <t>City coordinates</t>
+        </is>
+      </c>
+      <c r="B2" s="23" t="inlineStr">
+        <is>
+          <t>OpenStreetMap Nominatim</t>
+        </is>
+      </c>
+      <c r="C2" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D2" s="23" t="inlineStr">
+        <is>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="E2" s="23" t="inlineStr">
+        <is>
+          <t>Map position of any city, including typed-in 'Other' places</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>Real places</t>
+        </is>
+      </c>
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>OpenStreetMap Overpass</t>
+        </is>
+      </c>
+      <c r="C3" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D3" s="23" t="inlineStr">
+        <is>
+          <t>7 days</t>
+        </is>
+      </c>
+      <c r="E3" s="23" t="inlineStr">
+        <is>
+          <t>Cinemas, restaurants, stadiums, theatres, event venues, hotels, caterers, gift shops, attractions</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>Films</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Apple iTunes movie chart (country store)</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>6 hours</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>Popular films with posters; TMDB replaces it when TMDB_API_KEY is set</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>Films in cinemas</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>TMDB now playing</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>Free key (TMDB_API_KEY)</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>6 hours</t>
+        </is>
+      </c>
+      <c r="E5" s="23" t="inlineStr">
+        <is>
+          <t>Films actually showing in the country's cinemas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>Sports fixtures</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>TheSportsDB (public key 123)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D6" s="23" t="inlineStr">
+        <is>
+          <t>3 hours</t>
+        </is>
+      </c>
+      <c r="E6" s="23" t="inlineStr">
+        <is>
+          <t>IPL, ISL; NHL, NBA, MLB, MLS, CFL; Premier League</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Concerts &amp; shows</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>Ticketmaster Discovery</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>Free key (TICKETMASTER_API_KEY)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>3 hours</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="inlineStr">
+        <is>
+          <t>Real events and ticket price ranges near the city</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>Weather</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>Open-Meteo</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>1 hour</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>16-day forecast on the home page and events; also gives the city's time zone</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>Exchange rates</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>Frankfurter (ECB)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>12 hours</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>₹ shown alongside C$, US$, £, S$</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>Public holidays</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>Nager.Date (India: built-in list)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>7 days</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>Upcoming holidays, filtered by Canadian province</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>Showtimes, seat maps, payments</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Simulated</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>No free API publishes them; the payment gateway is a demo</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>If a source can't be reached, that part of the app falls back to labelled sample data. Set EOS_OFFLINE=1 to never call the network.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3119,249 +4064,274 @@
     </row>
     <row r="2">
       <c r="A2" s="23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="23" t="inlineStr">
         <is>
-          <t>Requester</t>
+          <t>Chat agent</t>
         </is>
       </c>
       <c r="C2" s="23" t="inlineStr">
         <is>
-          <t>Picks Country → State → City (or 'Other' and types it), then browses Movies / Events / Dining, or types a request such as '3 tickets for Orbit 9 IMAX tomorrow evening'.</t>
+          <t>Opening screen: the user types e.g. 'I'm planning to go for a movie today, can you check the theatres?'. The chat lists theatres near the city, then the films and showtimes at the chosen theatre, a seat map with the best seats preselected, who pays, the payment page, and the ticket.</t>
         </is>
       </c>
       <c r="D2" s="23" t="inlineStr">
         <is>
-          <t>Location + request</t>
+          <t>Conversation that calls the agents below</t>
         </is>
       </c>
       <c r="E2" s="23" t="inlineStr">
         <is>
-          <t>Top bar · Discover</t>
+          <t>Discover · Concierge chat</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="23" t="inlineStr">
         <is>
-          <t>Concierge agent</t>
+          <t>Requester</t>
         </is>
       </c>
       <c r="C3" s="23" t="inlineStr">
         <is>
-          <t>Works out the category, city, date and party size; picks the show and best seats together, the event and ticket tier, or the venue; prices it; proposes who pays; matches a family/friends group.</t>
+          <t>Picks Country → State → City (or 'Other' and types it), then browses Movies / Events / Dining, or types a request such as '3 tickets for Orbit 9 IMAX tomorrow evening'.</t>
         </is>
       </c>
       <c r="D3" s="23" t="inlineStr">
         <is>
-          <t>Priced booking draft</t>
+          <t>Location + request</t>
         </is>
       </c>
       <c r="E3" s="23" t="inlineStr">
         <is>
-          <t>Checkout · Concierge</t>
+          <t>Top bar · Discover</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="23" t="inlineStr">
         <is>
-          <t>Budget agent</t>
+          <t>Concierge agent</t>
         </is>
       </c>
       <c r="C4" s="23" t="inlineStr">
         <is>
-          <t>Checks the right pot: department quarterly budget, wellbeing allowance or personal monthly budget.</t>
+          <t>Works out the category, city, date and party size; picks the show and best seats together, the event and ticket tier, or the venue; prices it; proposes who pays; matches a family/friends group.</t>
         </is>
       </c>
       <c r="D4" s="23" t="inlineStr">
         <is>
-          <t>ok / warn / over + notes</t>
+          <t>Priced booking draft</t>
         </is>
       </c>
       <c r="E4" s="23" t="inlineStr">
         <is>
-          <t>Checkout · Budget agent</t>
+          <t>Checkout · Concierge</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="23" t="inlineStr">
         <is>
-          <t>Policy agent</t>
+          <t>Budget agent</t>
         </is>
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>Builds the approval chain from ₹ thresholds, per-person caps, compliance categories and budget status; removes self-approval.</t>
+          <t>Checks the right pot: department quarterly budget, wellbeing allowance or personal monthly budget.</t>
         </is>
       </c>
       <c r="D5" s="23" t="inlineStr">
         <is>
-          <t>Ordered approvers or auto-approval</t>
+          <t>ok / warn / over + notes</t>
         </is>
       </c>
       <c r="E5" s="23" t="inlineStr">
         <is>
-          <t>Checkout · Policy agent</t>
+          <t>Checkout · Budget agent</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>Requester</t>
+          <t>Policy agent</t>
         </is>
       </c>
       <c r="C6" s="23" t="inlineStr">
         <is>
-          <t>Changes who pays / group / purpose if needed and confirms. Movie seats are held immediately.</t>
+          <t>Builds the approval chain from ₹ thresholds, per-person caps, compliance categories and budget status; removes self-approval.</t>
         </is>
       </c>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t>Booking created</t>
+          <t>Ordered approvers or auto-approval</t>
         </is>
       </c>
       <c r="E6" s="23" t="inlineStr">
         <is>
-          <t>Bookings</t>
+          <t>Checkout · Policy agent</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>Approval agent</t>
+          <t>Requester</t>
         </is>
       </c>
       <c r="C7" s="23" t="inlineStr">
         <is>
-          <t>Notifies the current approver; each approves or rejects in order; a rejection stops the chain and releases seats.</t>
+          <t>Changes who pays / group / purpose if needed and confirms. Movie seats are held immediately.</t>
         </is>
       </c>
       <c r="D7" s="23" t="inlineStr">
         <is>
-          <t>Approved / rejected</t>
+          <t>Booking created</t>
         </is>
       </c>
       <c r="E7" s="23" t="inlineStr">
         <is>
-          <t>Approvals</t>
+          <t>Bookings</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>Booking agent</t>
+          <t>Approval agent</t>
         </is>
       </c>
       <c r="C8" s="23" t="inlineStr">
         <is>
-          <t>Confirms with the cinema, organiser or venue and issues m-tickets, e-tickets or a confirmation code.</t>
+          <t>Notifies the current approver; each approves or rejects in order; a rejection stops the chain and releases seats.</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
-          <t>Confirmed booking</t>
+          <t>Approved / rejected</t>
         </is>
       </c>
       <c r="E8" s="23" t="inlineStr">
         <is>
-          <t>Bookings → details</t>
+          <t>Approvals</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>Split agent</t>
+          <t>Booking agent</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>Shared bookings: posts to the group ledger, computes shares, balances and a fewest-payments settle-up (UPI).</t>
+          <t>Confirms with the cinema, organiser or venue and issues m-tickets, e-tickets or a confirmation code.</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
         <is>
-          <t>Group ledger entry</t>
+          <t>Confirmed booking</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
         <is>
-          <t>Family &amp; friends</t>
+          <t>Bookings → details</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>Expense agent</t>
+          <t>Split agent</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
         <is>
-          <t>Reimbursable bookings become claimable; the report is drafted with receipts and routed to Finance, HR or Benefits.</t>
+          <t>Shared bookings: posts to the group ledger, computes shares, balances and a fewest-payments settle-up (UPI).</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>Expense report</t>
+          <t>Group ledger entry</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
         <is>
-          <t>Expense reports</t>
+          <t>Family &amp; friends</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>Expense agent</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>Reimbursable bookings become claimable; the report is drafted with receipts and routed to Finance, HR or Benefits.</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>Expense report</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>Expense reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Finance / HR / Benefits</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>Final approval; reimbursement with payroll; the wellbeing allowance is reduced for wellbeing claims.</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>Reimbursed</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>Expense reports / Budgets &amp; spend</t>
         </is>
@@ -4422,7 +5392,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -4442,12 +5412,12 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Pushpaka Rising · IMAX · 8 tickets</t>
+          <t>Pushpaka Rising · 2D · 8 tickets</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
         <is>
-          <t>Starlight Multiplex — Hyderabad Central</t>
+          <t>Royal Screens Hyderabad</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
@@ -4489,7 +5459,7 @@
         <v>8</v>
       </c>
       <c r="P8" s="11" t="n">
-        <v>4160</v>
+        <v>1760</v>
       </c>
       <c r="Q8" s="13">
         <f>IF(O8&gt;0,P8/O8,0)</f>
@@ -4520,7 +5490,7 @@
       <c r="W8" s="8" t="inlineStr"/>
       <c r="X8" s="8" t="inlineStr">
         <is>
-          <t>IMAX · H4, H5, H6, H7, H8, H9, H10, H11</t>
+          <t>2D · D5, D6, D7, D8, D9, D10, D11, D12</t>
         </is>
       </c>
     </row>
@@ -6775,7 +7745,7 @@
       </c>
       <c r="K2" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23T00:00:35.488Z</t>
+          <t>2026-09-23T00:42:36.829Z</t>
         </is>
       </c>
     </row>
@@ -6826,7 +7796,7 @@
       </c>
       <c r="K3" s="8" t="inlineStr">
         <is>
-          <t>2026-09-23T00:00:35.488Z</t>
+          <t>2026-09-23T00:42:36.829Z</t>
         </is>
       </c>
     </row>
